--- a/config/sla_targets.xlsx
+++ b/config/sla_targets.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P.acquahrockson\Desktop\Sla-tracker\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8912D4F-7B20-4F32-8B91-2E955E8ACEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FD122C-B935-42E9-8C16-2C8C295FC7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Corporate" sheetId="1" r:id="rId1"/>
-    <sheet name="Retail" sheetId="2" r:id="rId2"/>
-    <sheet name="SMB" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Retail" sheetId="2" r:id="rId3"/>
+    <sheet name="SMB" sheetId="3" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$C$130</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="120">
   <si>
     <t>Name</t>
   </si>
@@ -393,6 +397,9 @@
   </si>
   <si>
     <t>The Bakery Technology Limited</t>
+  </si>
+  <si>
+    <t>NEW_GWCL</t>
   </si>
 </sst>
 </file>
@@ -740,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -1335,7 +1342,7 @@
       <c r="A54" t="s">
         <v>46</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="2">
@@ -1346,7 +1353,7 @@
       <c r="A55" t="s">
         <v>46</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2">
@@ -1355,1045 +1362,13 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56" t="s">
-        <v>47</v>
+        <v>37</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C56" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>46</v>
-      </c>
-      <c r="B64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>45</v>
-      </c>
-      <c r="B67" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>37</v>
-      </c>
-      <c r="B69" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>37</v>
-      </c>
-      <c r="B78" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>37</v>
-      </c>
-      <c r="B81" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>37</v>
-      </c>
-      <c r="B82" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>37</v>
-      </c>
-      <c r="B83" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>46</v>
-      </c>
-      <c r="B84" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>37</v>
-      </c>
-      <c r="B85" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>45</v>
-      </c>
-      <c r="B86" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>45</v>
-      </c>
-      <c r="B87" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>45</v>
-      </c>
-      <c r="B88" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>83</v>
-      </c>
-      <c r="B89" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>37</v>
-      </c>
-      <c r="B90" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>37</v>
-      </c>
-      <c r="B91" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>37</v>
-      </c>
-      <c r="B92" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>45</v>
-      </c>
-      <c r="B93" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>45</v>
-      </c>
-      <c r="B94" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>37</v>
-      </c>
-      <c r="B95" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>45</v>
-      </c>
-      <c r="B96" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>37</v>
-      </c>
-      <c r="B97" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>37</v>
-      </c>
-      <c r="B98" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>37</v>
-      </c>
-      <c r="B99" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>46</v>
-      </c>
-      <c r="B100" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>37</v>
-      </c>
-      <c r="B101" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>37</v>
-      </c>
-      <c r="B102" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>37</v>
-      </c>
-      <c r="B103" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>45</v>
-      </c>
-      <c r="B104" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>45</v>
-      </c>
-      <c r="B105" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>37</v>
-      </c>
-      <c r="B106" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>37</v>
-      </c>
-      <c r="B107" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>37</v>
-      </c>
-      <c r="B108" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>45</v>
-      </c>
-      <c r="B109" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>37</v>
-      </c>
-      <c r="B110" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>46</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>45</v>
-      </c>
-      <c r="B112" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>37</v>
-      </c>
-      <c r="B113" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>83</v>
-      </c>
-      <c r="B114" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>46</v>
-      </c>
-      <c r="B115" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>37</v>
-      </c>
-      <c r="B116" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>45</v>
-      </c>
-      <c r="B117" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>37</v>
-      </c>
-      <c r="B118" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>37</v>
-      </c>
-      <c r="B119" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>37</v>
-      </c>
-      <c r="B120" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>37</v>
-      </c>
-      <c r="B121" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>45</v>
-      </c>
-      <c r="B122" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>37</v>
-      </c>
-      <c r="B123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>45</v>
-      </c>
-      <c r="B124" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>37</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>37</v>
-      </c>
-      <c r="B126" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>37</v>
-      </c>
-      <c r="B127" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>37</v>
-      </c>
-      <c r="B128" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>37</v>
-      </c>
-      <c r="B129" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>37</v>
-      </c>
-      <c r="B130" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>45</v>
-      </c>
-      <c r="B131" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>45</v>
-      </c>
-      <c r="B132" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>45</v>
-      </c>
-      <c r="B133" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>45</v>
-      </c>
-      <c r="B134" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>45</v>
-      </c>
-      <c r="B135" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>45</v>
-      </c>
-      <c r="B136" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>83</v>
-      </c>
-      <c r="B137" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>45</v>
-      </c>
-      <c r="B138" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>46</v>
-      </c>
-      <c r="B139" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>83</v>
-      </c>
-      <c r="B140" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>37</v>
-      </c>
-      <c r="B141" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>37</v>
-      </c>
-      <c r="B142" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>45</v>
-      </c>
-      <c r="B143" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>37</v>
-      </c>
-      <c r="B144" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>45</v>
-      </c>
-      <c r="B145" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>37</v>
-      </c>
-      <c r="B146" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>37</v>
-      </c>
-      <c r="B147" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>37</v>
-      </c>
-      <c r="B148" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>45</v>
-      </c>
-      <c r="B149" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>45</v>
-      </c>
-      <c r="B150" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>46</v>
-      </c>
-      <c r="B151" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>83</v>
-      </c>
-      <c r="B152" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>37</v>
-      </c>
-      <c r="B153" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>45</v>
-      </c>
-      <c r="B154" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>37</v>
-      </c>
-      <c r="B155" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>37</v>
-      </c>
-      <c r="B156" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>37</v>
-      </c>
-      <c r="B157" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>45</v>
-      </c>
-      <c r="B158" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>45</v>
-      </c>
-      <c r="B159" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>37</v>
-      </c>
-      <c r="B160" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>45</v>
-      </c>
-      <c r="B161" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>45</v>
-      </c>
-      <c r="B162" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>37</v>
-      </c>
-      <c r="B163" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>45</v>
-      </c>
-      <c r="B164" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>45</v>
-      </c>
-      <c r="B165" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
-        <v>37</v>
-      </c>
-      <c r="B166" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>45</v>
-      </c>
-      <c r="B167" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>46</v>
-      </c>
-      <c r="B168" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>37</v>
-      </c>
-      <c r="B169" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>37</v>
-      </c>
-      <c r="B170" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>37</v>
-      </c>
-      <c r="B171" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
-        <v>37</v>
-      </c>
-      <c r="B172" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>37</v>
-      </c>
-      <c r="B173" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
-        <v>37</v>
-      </c>
-      <c r="B174" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>37</v>
-      </c>
-      <c r="B175" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
-        <v>37</v>
-      </c>
-      <c r="B176" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>45</v>
-      </c>
-      <c r="B177" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>37</v>
-      </c>
-      <c r="B178" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>37</v>
-      </c>
-      <c r="B179" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>45</v>
-      </c>
-      <c r="B180" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>37</v>
-      </c>
-      <c r="B181" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>37</v>
-      </c>
-      <c r="B182" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>37</v>
-      </c>
-      <c r="B183" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>46</v>
-      </c>
-      <c r="B184" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>37</v>
-      </c>
-      <c r="B185" t="s">
-        <v>103</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -2402,6 +1377,1198 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFEA6B2-9D01-4B24-AA77-47F03E8B424F}">
+  <dimension ref="A1:C130"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" t="s">
+        <v>85</v>
+      </c>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" t="s">
+        <v>92</v>
+      </c>
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" t="s">
+        <v>93</v>
+      </c>
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>46</v>
+      </c>
+      <c r="B74" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" t="s">
+        <v>98</v>
+      </c>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" t="s">
+        <v>99</v>
+      </c>
+      <c r="C76" s="2"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>45</v>
+      </c>
+      <c r="B77" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" s="2"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" s="2"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>45</v>
+      </c>
+      <c r="B79" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" s="2"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" s="2"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="2"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>37</v>
+      </c>
+      <c r="B82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="2"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="2"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>37</v>
+      </c>
+      <c r="B84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C84" s="2"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>45</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" s="2"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>37</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" s="2"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" s="2"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>37</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" s="2"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>37</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" s="2"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>45</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" s="2"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>46</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" s="2"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>83</v>
+      </c>
+      <c r="B92" t="s">
+        <v>108</v>
+      </c>
+      <c r="C92" s="2"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" t="s">
+        <v>87</v>
+      </c>
+      <c r="C93" s="2"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>37</v>
+      </c>
+      <c r="B94" t="s">
+        <v>87</v>
+      </c>
+      <c r="C94" s="2"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" t="s">
+        <v>78</v>
+      </c>
+      <c r="C95" s="2"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>46</v>
+      </c>
+      <c r="B96" t="s">
+        <v>78</v>
+      </c>
+      <c r="C96" s="2"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>45</v>
+      </c>
+      <c r="B97" t="s">
+        <v>78</v>
+      </c>
+      <c r="C97" s="2"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>37</v>
+      </c>
+      <c r="B98" t="s">
+        <v>79</v>
+      </c>
+      <c r="C98" s="2"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>45</v>
+      </c>
+      <c r="B99" t="s">
+        <v>79</v>
+      </c>
+      <c r="C99" s="2"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>37</v>
+      </c>
+      <c r="B100" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100" s="2"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>45</v>
+      </c>
+      <c r="B101" t="s">
+        <v>27</v>
+      </c>
+      <c r="C101" s="2"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>37</v>
+      </c>
+      <c r="B102" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" s="2"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>83</v>
+      </c>
+      <c r="B103" t="s">
+        <v>100</v>
+      </c>
+      <c r="C103" s="2"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>45</v>
+      </c>
+      <c r="B104" t="s">
+        <v>80</v>
+      </c>
+      <c r="C104" s="2"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>45</v>
+      </c>
+      <c r="B105" t="s">
+        <v>101</v>
+      </c>
+      <c r="C105" s="2"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" t="s">
+        <v>81</v>
+      </c>
+      <c r="C106" s="2"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>37</v>
+      </c>
+      <c r="B107" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" s="2"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108" s="2"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>45</v>
+      </c>
+      <c r="B109" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109" s="2"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>37</v>
+      </c>
+      <c r="B110" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110" s="2"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>37</v>
+      </c>
+      <c r="B111" t="s">
+        <v>96</v>
+      </c>
+      <c r="C111" s="2"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>37</v>
+      </c>
+      <c r="B112" t="s">
+        <v>97</v>
+      </c>
+      <c r="C112" s="2"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>45</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" s="2"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>37</v>
+      </c>
+      <c r="B114" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" s="2"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>37</v>
+      </c>
+      <c r="B115" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115" s="2"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>46</v>
+      </c>
+      <c r="B116" t="s">
+        <v>47</v>
+      </c>
+      <c r="C116" s="2"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" t="s">
+        <v>102</v>
+      </c>
+      <c r="C117" s="2"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>46</v>
+      </c>
+      <c r="B118" t="s">
+        <v>118</v>
+      </c>
+      <c r="C118" s="2"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>37</v>
+      </c>
+      <c r="B119" t="s">
+        <v>110</v>
+      </c>
+      <c r="C119" s="2"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>83</v>
+      </c>
+      <c r="B120" t="s">
+        <v>82</v>
+      </c>
+      <c r="C120" s="2"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B121" t="s">
+        <v>33</v>
+      </c>
+      <c r="C121" s="2"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>37</v>
+      </c>
+      <c r="B122" t="s">
+        <v>34</v>
+      </c>
+      <c r="C122" s="2"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>45</v>
+      </c>
+      <c r="B123" t="s">
+        <v>34</v>
+      </c>
+      <c r="C123" s="2"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>37</v>
+      </c>
+      <c r="B124" t="s">
+        <v>35</v>
+      </c>
+      <c r="C124" s="2"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>45</v>
+      </c>
+      <c r="B125" t="s">
+        <v>103</v>
+      </c>
+      <c r="C125" s="2"/>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>37</v>
+      </c>
+      <c r="B126" t="s">
+        <v>103</v>
+      </c>
+      <c r="C126" s="2"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>37</v>
+      </c>
+      <c r="B127" t="s">
+        <v>109</v>
+      </c>
+      <c r="C127" s="2"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>45</v>
+      </c>
+      <c r="B128" t="s">
+        <v>109</v>
+      </c>
+      <c r="C128" s="2"/>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129" t="s">
+        <v>36</v>
+      </c>
+      <c r="C129" s="2"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>45</v>
+      </c>
+      <c r="B130" t="s">
+        <v>36</v>
+      </c>
+      <c r="C130" s="2"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C130" xr:uid="{DBFEA6B2-9D01-4B24-AA77-47F03E8B424F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C130">
+      <sortCondition ref="B1:B130"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD885731-E7FF-435C-A9B2-169479FA08B2}">
   <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2587,52 +2754,60 @@
         <v>2.9820293494467551E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.7066593849199577E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" s="1"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.35">
@@ -2703,7 +2878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5CBF6E-F7B9-466C-B37D-4BDA5D3DB5E8}">
   <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2824,7 +2999,15 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="1"/>
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1.7066593849199577E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>

--- a/config/sla_targets.xlsx
+++ b/config/sla_targets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P.acquahrockson\Desktop\Sla-tracker\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FD122C-B935-42E9-8C16-2C8C295FC7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1ED48A-D196-4F95-8938-EA229DFB97C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,8 @@
     <sheet name="SMB" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$C$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Corporate!$A$1:$C$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$R$133</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="146">
   <si>
     <t>Name</t>
   </si>
@@ -400,17 +401,96 @@
   </si>
   <si>
     <t>NEW_GWCL</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Rate %</t>
+  </si>
+  <si>
+    <t>2001-1000000</t>
+  </si>
+  <si>
+    <t>SLA start</t>
+  </si>
+  <si>
+    <t>SLA end</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>SLA NA</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Card%</t>
+  </si>
+  <si>
+    <t>101-1000.99(%)</t>
+  </si>
+  <si>
+    <t>1001-2000.99(%)</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>tiered</t>
+  </si>
+  <si>
+    <t>Rate GHC</t>
+  </si>
+  <si>
+    <t>Bank(GHC)</t>
+  </si>
+  <si>
+    <t>Capped(GHC)</t>
+  </si>
+  <si>
+    <t>1-50.99(GHC)</t>
+  </si>
+  <si>
+    <t>51-100.99(GHC)</t>
+  </si>
+  <si>
+    <t>101-1000.99(GHC)</t>
+  </si>
+  <si>
+    <t>1001-2000.99(GHC)</t>
+  </si>
+  <si>
+    <t>DEVPLUSE TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>Jesi Education Technology Ltd.</t>
+  </si>
+  <si>
+    <t>Progressive Security Co. Ltd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,6 +499,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -452,11 +540,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -466,12 +555,154 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -482,6 +713,36 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{539B56AE-C277-47EC-94C7-F16FE2A5778C}" name="Table1" displayName="Table1" ref="A1:R133" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A1:R133" xr:uid="{DBFEA6B2-9D01-4B24-AA77-47F03E8B424F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R133">
+    <sortCondition ref="B1:B133"/>
+  </sortState>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{47B02190-EED4-4B9A-BD89-AFBBE4A8C20B}" name="service"/>
+    <tableColumn id="2" xr3:uid="{EF45BA29-A457-4D23-BC22-84BBDBB7C89C}" name="Client"/>
+    <tableColumn id="3" xr3:uid="{2DE86EC4-6604-4181-B0E7-54F309000BAD}" name="Type"/>
+    <tableColumn id="4" xr3:uid="{DD578595-7609-4929-87C1-C632796116AE}" name="Rate %" dataDxfId="5" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{54EABEFF-98E6-4AC6-AA42-A27D73265558}" name="Capped(GHC)" dataDxfId="4" dataCellStyle="Percent"/>
+    <tableColumn id="6" xr3:uid="{86803708-5869-460C-AB88-80E22934B585}" name="Rate GHC" dataDxfId="3" dataCellStyle="Percent"/>
+    <tableColumn id="7" xr3:uid="{D6D59741-6F9C-457A-B699-39F04F508A3D}" name="1-50.99(GHC)"/>
+    <tableColumn id="8" xr3:uid="{F00D4508-42CA-4140-96C4-2927A1CB8577}" name="51-100.99(GHC)"/>
+    <tableColumn id="9" xr3:uid="{D3B3A3D8-5AB5-464B-B906-482B62B2198F}" name="101-1000.99(GHC)"/>
+    <tableColumn id="10" xr3:uid="{BDF22EB3-FC9A-4B26-84FB-BBE3DDC564AB}" name="101-1000.99(%)"/>
+    <tableColumn id="11" xr3:uid="{F31ED1FD-C712-4459-AD13-98C8CC6F5D95}" name="1001-2000.99(%)" dataDxfId="2" dataCellStyle="Percent"/>
+    <tableColumn id="18" xr3:uid="{B81F3138-F40E-49FD-AD79-EE7E5B77C13C}" name="1001-2000.99(GHC)" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="12" xr3:uid="{49CE33E1-A934-432A-A6D7-89406C003D2C}" name="2001-1000000"/>
+    <tableColumn id="13" xr3:uid="{D3E02E61-056A-4526-97FB-A7C813ABCB5B}" name="Card%" dataDxfId="0" dataCellStyle="Percent"/>
+    <tableColumn id="14" xr3:uid="{18798627-0106-41A2-AD65-17EFAB413212}" name="Bank(GHC)"/>
+    <tableColumn id="15" xr3:uid="{9E803BBD-2A14-4C07-9333-033B2E0A1B7F}" name="SLA start"/>
+    <tableColumn id="16" xr3:uid="{2FE62DA3-98AF-4526-8699-5C55F9891691}" name="SLA end"/>
+    <tableColumn id="17" xr3:uid="{E0A7B368-FB59-4513-821F-CF27B84C0EC7}" name="Comment"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -747,12 +1008,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -762,7 +1023,7 @@
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
     </row>
@@ -771,21 +1032,22 @@
         <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.05</v>
+        <v>95</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0.02</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1.4999999999999998E-2</v>
+        <v>38</v>
+      </c>
+      <c r="C3" s="12">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -793,21 +1055,21 @@
         <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1.5000000000000005E-2</v>
+        <v>3</v>
+      </c>
+      <c r="C4" s="12">
+        <v>0.05</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1.5000000000000003E-2</v>
+        <v>39</v>
+      </c>
+      <c r="C5" s="12">
+        <v>5.000000000000001E-3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -815,10 +1077,10 @@
         <v>37</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1.4999999999999999E-2</v>
+        <v>4</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1.4999999999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -826,21 +1088,23 @@
         <v>37</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2">
+        <v>89</v>
+      </c>
+      <c r="C7" s="12">
+        <f>1.5%</f>
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2">
-        <v>9.9999999999999985E-3</v>
+        <v>89</v>
+      </c>
+      <c r="C8" s="12">
+        <f>1%</f>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -848,10 +1112,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="C9" s="12">
+        <v>1.5000000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -859,10 +1123,10 @@
         <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.01</v>
+        <v>6</v>
+      </c>
+      <c r="C10" s="12">
+        <v>1.5000000000000003E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -870,21 +1134,23 @@
         <v>37</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1.1999999999999999E-2</v>
+        <v>143</v>
+      </c>
+      <c r="C11" s="12">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1.0000000000000963E-2</v>
+        <v>143</v>
+      </c>
+      <c r="C12" s="12">
+        <f>1%</f>
+        <v>0.01</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -892,10 +1158,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1.7999999999999947E-2</v>
+        <v>7</v>
+      </c>
+      <c r="C13" s="12">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -903,32 +1169,33 @@
         <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1.2499999999999999E-2</v>
+        <v>114</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0.02</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2">
+        <v>40</v>
+      </c>
+      <c r="C15" s="12">
+        <f>1.5%</f>
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2.0000000000000011E-2</v>
+        <v>41</v>
+      </c>
+      <c r="C16" s="12">
+        <v>3.0919741680237212E-3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -936,10 +1203,10 @@
         <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="C17" s="12">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -947,32 +1214,32 @@
         <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1.499999999999998E-2</v>
+        <v>9</v>
+      </c>
+      <c r="C18" s="12">
+        <v>9.9999999999999985E-3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1.4999999999999999E-2</v>
+        <v>9</v>
+      </c>
+      <c r="C19" s="12">
+        <v>3.3075860458781641E-3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1.499999999999998E-2</v>
+        <v>9</v>
+      </c>
+      <c r="C20" s="12">
+        <v>0.19421428571428576</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -980,10 +1247,10 @@
         <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="2">
-        <v>9.0365061432001129E-3</v>
+        <v>10</v>
+      </c>
+      <c r="C21" s="12">
+        <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -991,21 +1258,21 @@
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0.01</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1.4999999999999999E-2</v>
+        <v>11</v>
+      </c>
+      <c r="C23" s="12">
+        <v>4.9999999999999992E-3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -1013,21 +1280,21 @@
         <v>37</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1.5000000000000048E-2</v>
+        <v>12</v>
+      </c>
+      <c r="C24" s="12">
+        <v>1.1999999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1.3000000000000001E-2</v>
+        <v>12</v>
+      </c>
+      <c r="C25" s="12">
+        <v>5.000000000000001E-3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -1035,10 +1302,10 @@
         <v>37</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1.5000000000000001E-2</v>
+        <v>13</v>
+      </c>
+      <c r="C26" s="12">
+        <v>1.0000000000000963E-2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -1046,21 +1313,21 @@
         <v>37</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="2">
-        <v>4.4999999999999991E-2</v>
+        <v>14</v>
+      </c>
+      <c r="C27" s="12">
+        <v>1.7999999999999947E-2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="2">
-        <v>1.4999999999999999E-2</v>
+        <v>14</v>
+      </c>
+      <c r="C28" s="12">
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -1068,10 +1335,11 @@
         <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="2">
-        <v>1.999999999999999E-2</v>
+        <v>144</v>
+      </c>
+      <c r="C29" s="12">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -1079,21 +1347,21 @@
         <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1.4999999999999999E-2</v>
+        <v>15</v>
+      </c>
+      <c r="C30" s="12">
+        <v>1.2499999999999999E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1.4999999999999999E-2</v>
+        <v>42</v>
+      </c>
+      <c r="C31" s="12">
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -1101,10 +1369,11 @@
         <v>37</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="2">
-        <v>0.5</v>
+        <v>42</v>
+      </c>
+      <c r="C32" s="12">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -1112,21 +1381,21 @@
         <v>37</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1.7500000000000002E-2</v>
+        <v>16</v>
+      </c>
+      <c r="C33" s="12">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="2">
-        <v>0.02</v>
+        <v>16</v>
+      </c>
+      <c r="C34" s="12">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -1134,21 +1403,21 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="2">
-        <v>1.8499999999999978E-2</v>
+        <v>76</v>
+      </c>
+      <c r="C35" s="12">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="2">
-        <v>3.6869826937547027E-3</v>
+        <v>17</v>
+      </c>
+      <c r="C36" s="12">
+        <v>2.0000000000000011E-2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -1156,54 +1425,55 @@
         <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="2">
-        <v>5.000000000000001E-3</v>
+        <v>43</v>
+      </c>
+      <c r="C37" s="12">
+        <v>4.3165203929834859E-3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="2">
-        <v>1.7443590456863624E-4</v>
+        <v>18</v>
+      </c>
+      <c r="C38" s="12">
+        <f>1.85%</f>
+        <v>1.8500000000000003E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="2">
-        <v>3.0919741680237212E-3</v>
+        <v>19</v>
+      </c>
+      <c r="C39" s="12">
+        <v>1.499999999999998E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="2">
-        <v>3.3075860458781641E-3</v>
+        <v>20</v>
+      </c>
+      <c r="C40" s="12">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="2">
-        <v>4.9999999999999992E-3</v>
+        <v>21</v>
+      </c>
+      <c r="C41" s="12">
+        <v>1.499999999999998E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -1211,32 +1481,32 @@
         <v>45</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="2">
-        <v>5.000000000000001E-3</v>
+        <v>44</v>
+      </c>
+      <c r="C42" s="12">
+        <v>9.0244562765093403E-4</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="2">
-        <v>4.3851189477805383E-4</v>
+        <v>22</v>
+      </c>
+      <c r="C43" s="12">
+        <v>9.0365061432001129E-3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C44" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>23</v>
+      </c>
+      <c r="C44" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -1244,21 +1514,21 @@
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C45" s="2">
-        <v>4.3165203929834859E-3</v>
+        <v>23</v>
+      </c>
+      <c r="C45" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" s="2">
-        <v>9.0244562765093403E-4</v>
+        <v>24</v>
+      </c>
+      <c r="C46" s="12">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -1266,54 +1536,55 @@
         <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="2">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="C47" s="12">
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="2">
+        <v>145</v>
+      </c>
+      <c r="C48" s="12">
+        <f>0.5%</f>
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" s="2">
-        <v>9.9751243781094519E-3</v>
+        <v>25</v>
+      </c>
+      <c r="C49" s="12">
+        <v>1.5000000000000048E-2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>26</v>
+      </c>
+      <c r="C50" s="12">
+        <v>1.3000000000000001E-2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" s="2">
-        <v>3.3025099075297227E-3</v>
+        <v>27</v>
+      </c>
+      <c r="C51" s="12">
+        <v>1.5000000000000001E-2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -1321,43 +1592,43 @@
         <v>45</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C52" s="2">
-        <v>2.9999999999999992E-3</v>
+        <v>27</v>
+      </c>
+      <c r="C52" s="12">
+        <v>9.9751243781094519E-3</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C53" s="2">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="C53" s="12">
+        <v>4.4999999999999991E-2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="2">
-        <v>0.19421428571428576</v>
+        <v>29</v>
+      </c>
+      <c r="C54" s="12">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" s="2">
-        <v>7.1960461285008215E-2</v>
+        <v>29</v>
+      </c>
+      <c r="C55" s="12">
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -1365,1206 +1636,1995 @@
         <v>37</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="2">
+        <v>30</v>
+      </c>
+      <c r="C56" s="12">
+        <v>1.999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="12">
+        <f>0.55%</f>
+        <v>5.5000000000000005E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" s="12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="12">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" s="12">
+        <v>1.7500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" s="12">
+        <v>2.9999999999999992E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" s="12">
         <v>0.02</v>
       </c>
     </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" s="12">
+        <f>1.75%</f>
+        <v>1.7500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="12">
+        <v>1.8499999999999978E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>45</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="12">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" s="12">
+        <f>0.05%</f>
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:C56" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C66">
+      <sortCondition ref="B1:B56"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFEA6B2-9D01-4B24-AA77-47F03E8B424F}">
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:R133"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="10.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.90625" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" customWidth="1"/>
+    <col min="9" max="9" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.08984375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.90625" customWidth="1"/>
+    <col min="16" max="17" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>37</v>
       </c>
       <c r="B2" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="N2" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="5">
+        <v>45912</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>46642</v>
+      </c>
+      <c r="R2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>45</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="R3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>37</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="P4" s="5">
+        <v>45866</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>46596</v>
+      </c>
+      <c r="R4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>37</v>
       </c>
       <c r="B5" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="P5" s="5">
+        <v>45866</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>46596</v>
+      </c>
+      <c r="R5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="7">
+        <v>-0.02</v>
+      </c>
+      <c r="O6" s="6"/>
+      <c r="P6" s="5">
+        <v>45001</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>45732</v>
+      </c>
+      <c r="R6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>45</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="R7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N8" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="O8" s="6"/>
+      <c r="P8" s="5">
+        <v>45001</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>45732</v>
+      </c>
+      <c r="R8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1.5</v>
+      </c>
+      <c r="J9" s="6">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K9" s="7">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M9">
+        <v>30</v>
+      </c>
+      <c r="N9" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="O9" s="6"/>
+      <c r="P9" s="5">
+        <v>45993</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>46724</v>
+      </c>
+      <c r="R9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="M10">
+        <v>20</v>
+      </c>
+      <c r="O10" s="6"/>
+      <c r="P10" s="5">
+        <v>45993</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>46724</v>
+      </c>
+      <c r="R10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="P11" s="5">
+        <v>45993</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>46724</v>
+      </c>
+      <c r="R11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
+      <c r="P12" s="5">
+        <v>43550</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>44646</v>
+      </c>
+      <c r="R12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="7">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="P13" s="5">
+        <v>45127</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>45858</v>
+      </c>
+      <c r="R13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>134</v>
+      </c>
+      <c r="P14" s="5">
+        <v>45127</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>45858</v>
+      </c>
+      <c r="R14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N15" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="P15" s="5">
+        <v>45800</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>46530</v>
+      </c>
+      <c r="R15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N16" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="P16" s="5">
+        <v>45330</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>46061</v>
+      </c>
+      <c r="R16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="R17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>37</v>
       </c>
       <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="R18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="R19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P20" s="5">
+        <v>45127</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>45858</v>
+      </c>
+      <c r="R20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2</v>
+      </c>
+      <c r="N21" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="P21" s="5">
+        <v>45127</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>45858</v>
+      </c>
+      <c r="R21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="R22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="R23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="R24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C25" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1.5</v>
+      </c>
+      <c r="K25" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M25">
+        <v>30</v>
+      </c>
+      <c r="P25" s="5">
+        <v>45994</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>46724</v>
+      </c>
+      <c r="R25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N26" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="P26" s="5">
+        <v>45127</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>45858</v>
+      </c>
+      <c r="R26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O27">
+        <v>3</v>
+      </c>
+      <c r="P27" s="5">
+        <v>45778</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>46507</v>
+      </c>
+      <c r="R27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="P28" s="5">
+        <v>44042</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>45503</v>
+      </c>
+      <c r="R28" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P29" s="5">
+        <v>44312</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>46503</v>
+      </c>
+      <c r="R29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C30" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P30" s="5">
+        <v>44312</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>46503</v>
+      </c>
+      <c r="R30" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="C31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N31" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="P31" s="5">
+        <v>44970</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>45701</v>
+      </c>
+      <c r="R31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C32" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N32" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="P32" s="5">
+        <v>45127</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>45858</v>
+      </c>
+      <c r="R32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E33" s="8">
+        <v>25</v>
+      </c>
+      <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="P33" s="5">
+        <v>45493</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>46223</v>
+      </c>
+      <c r="R33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="8">
+        <v>1</v>
+      </c>
+      <c r="P34" s="5">
+        <v>45493</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>46223</v>
+      </c>
+      <c r="R34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="P35" s="5">
+        <v>45493</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>46223</v>
+      </c>
+      <c r="R35" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="P36" s="5">
+        <v>45493</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>46223</v>
+      </c>
+      <c r="R36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E37" s="8">
         <v>10</v>
       </c>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="P37" s="5">
+        <v>46057</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>46787</v>
+      </c>
+      <c r="R37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="7">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="P38" s="5">
+        <v>46057</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>46787</v>
+      </c>
+      <c r="R38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="C39" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0</v>
+      </c>
+      <c r="P39" s="5">
+        <v>45858</v>
+      </c>
+      <c r="Q39" s="5">
+        <v>46588</v>
+      </c>
+      <c r="R39" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="C40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1.95E-2</v>
+      </c>
+      <c r="P40" s="5">
+        <v>45858</v>
+      </c>
+      <c r="Q40" s="5">
+        <v>46588</v>
+      </c>
+      <c r="R40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="C41" t="s">
+        <v>134</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0</v>
+      </c>
+      <c r="P41" s="5">
+        <v>44885</v>
+      </c>
+      <c r="Q41" s="5">
+        <v>45626</v>
+      </c>
+      <c r="R41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="C42" t="s">
+        <v>135</v>
+      </c>
+      <c r="G42">
+        <v>0.5</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="L42" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="M42">
+        <v>10</v>
+      </c>
+      <c r="P42" s="5">
+        <v>45897</v>
+      </c>
+      <c r="Q42" s="5">
+        <v>46627</v>
+      </c>
+      <c r="R42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="R43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="2"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="R44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="C45" t="s">
+        <v>135</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="K45" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M45">
+        <v>30</v>
+      </c>
+      <c r="P45" s="5">
+        <v>45971</v>
+      </c>
+      <c r="Q45" s="5">
+        <v>46701</v>
+      </c>
+      <c r="R45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="C46" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P46" s="5">
+        <v>44835</v>
+      </c>
+      <c r="Q46" s="5">
+        <v>45566</v>
+      </c>
+      <c r="R46" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
         <v>11</v>
       </c>
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="C47" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P47" s="5">
+        <v>44835</v>
+      </c>
+      <c r="Q47" s="5">
+        <v>45566</v>
+      </c>
+      <c r="R47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="C48" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1.2E-2</v>
+      </c>
+      <c r="N48" s="7">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P48" s="5">
+        <v>45537</v>
+      </c>
+      <c r="Q48" s="5">
+        <v>46267</v>
+      </c>
+      <c r="R48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="P49" s="5">
+        <v>45537</v>
+      </c>
+      <c r="Q49" s="5">
+        <v>46267</v>
+      </c>
+      <c r="R49" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="R50" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="2"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" t="s">
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="2"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" t="s">
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" t="s">
         <v>84</v>
       </c>
-      <c r="C51" s="2"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" t="s">
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="2"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" t="s">
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" t="s">
         <v>85</v>
       </c>
-      <c r="C53" s="2"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" t="s">
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" t="s">
         <v>85</v>
       </c>
-      <c r="C54" s="2"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" t="s">
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="2"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" t="s">
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="2"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" t="s">
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="2"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>46</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B60" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="2"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" t="s">
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" t="s">
         <v>16</v>
       </c>
-      <c r="C59" s="2"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" t="s">
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" t="s">
         <v>76</v>
       </c>
-      <c r="C60" s="2"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" t="s">
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="2"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" t="s">
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" t="s">
         <v>117</v>
       </c>
-      <c r="C62" s="2"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" t="s">
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
         <v>106</v>
       </c>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" t="s">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>45</v>
+      </c>
+      <c r="B66" t="s">
         <v>43</v>
       </c>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" t="s">
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="2"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" t="s">
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="2"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" t="s">
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
         <v>20</v>
       </c>
-      <c r="C67" s="2"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>45</v>
-      </c>
-      <c r="B68" t="s">
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>45</v>
+      </c>
+      <c r="B70" t="s">
         <v>20</v>
       </c>
-      <c r="C68" s="2"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" t="s">
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" t="s">
         <v>77</v>
       </c>
-      <c r="C69" s="2"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" t="s">
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" t="s">
         <v>77</v>
       </c>
-      <c r="C70" s="2"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" t="s">
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="2"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" t="s">
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" t="s">
         <v>92</v>
       </c>
-      <c r="C72" s="2"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>83</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B75" t="s">
         <v>93</v>
       </c>
-      <c r="C73" s="2"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>46</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B76" t="s">
         <v>94</v>
       </c>
-      <c r="C74" s="2"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" t="s">
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="2"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" t="s">
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" t="s">
         <v>99</v>
       </c>
-      <c r="C76" s="2"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" t="s">
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>45</v>
+      </c>
+      <c r="B79" t="s">
         <v>44</v>
       </c>
-      <c r="C77" s="2"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>37</v>
-      </c>
-      <c r="B78" t="s">
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" t="s">
         <v>86</v>
       </c>
-      <c r="C78" s="2"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" t="s">
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" t="s">
         <v>107</v>
       </c>
-      <c r="C79" s="2"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" t="s">
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>37</v>
+      </c>
+      <c r="B82" t="s">
         <v>22</v>
       </c>
-      <c r="C80" s="2"/>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" t="s">
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" t="s">
         <v>22</v>
       </c>
-      <c r="C81" s="2"/>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>37</v>
-      </c>
-      <c r="B82" t="s">
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>37</v>
+      </c>
+      <c r="B84" t="s">
         <v>23</v>
       </c>
-      <c r="C82" s="2"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" t="s">
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>45</v>
+      </c>
+      <c r="B85" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="2"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>37</v>
-      </c>
-      <c r="B84" t="s">
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>37</v>
+      </c>
+      <c r="B86" t="s">
         <v>104</v>
       </c>
-      <c r="C84" s="2"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>45</v>
-      </c>
-      <c r="B85" t="s">
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" t="s">
         <v>24</v>
       </c>
-      <c r="C85" s="2"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>37</v>
-      </c>
-      <c r="B86" t="s">
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>37</v>
+      </c>
+      <c r="B88" t="s">
         <v>24</v>
       </c>
-      <c r="C86" s="2"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>45</v>
-      </c>
-      <c r="B87" t="s">
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>45</v>
+      </c>
+      <c r="B89" t="s">
         <v>25</v>
       </c>
-      <c r="C87" s="2"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>37</v>
-      </c>
-      <c r="B88" t="s">
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" t="s">
         <v>25</v>
       </c>
-      <c r="C88" s="2"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>37</v>
-      </c>
-      <c r="B89" t="s">
-        <v>26</v>
-      </c>
-      <c r="C89" s="2"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>45</v>
-      </c>
-      <c r="B90" t="s">
-        <v>26</v>
-      </c>
-      <c r="C90" s="2"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B91" t="s">
         <v>26</v>
       </c>
-      <c r="C91" s="2"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
+        <v>45</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>46</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>83</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B94" t="s">
         <v>108</v>
       </c>
-      <c r="C92" s="2"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>45</v>
-      </c>
-      <c r="B93" t="s">
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>45</v>
+      </c>
+      <c r="B95" t="s">
         <v>87</v>
       </c>
-      <c r="C93" s="2"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>37</v>
-      </c>
-      <c r="B94" t="s">
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>37</v>
+      </c>
+      <c r="B96" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="2"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>37</v>
-      </c>
-      <c r="B95" t="s">
-        <v>78</v>
-      </c>
-      <c r="C95" s="2"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>46</v>
-      </c>
-      <c r="B96" t="s">
-        <v>78</v>
-      </c>
-      <c r="C96" s="2"/>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B97" t="s">
         <v>78</v>
       </c>
-      <c r="C97" s="2"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B98" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>45</v>
+      </c>
+      <c r="B99" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>37</v>
+      </c>
+      <c r="B100" t="s">
         <v>79</v>
       </c>
-      <c r="C98" s="2"/>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>45</v>
-      </c>
-      <c r="B99" t="s">
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>45</v>
+      </c>
+      <c r="B101" t="s">
         <v>79</v>
       </c>
-      <c r="C99" s="2"/>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>37</v>
-      </c>
-      <c r="B100" t="s">
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>37</v>
+      </c>
+      <c r="B102" t="s">
         <v>27</v>
       </c>
-      <c r="C100" s="2"/>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>45</v>
-      </c>
-      <c r="B101" t="s">
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>45</v>
+      </c>
+      <c r="B103" t="s">
         <v>27</v>
       </c>
-      <c r="C101" s="2"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>37</v>
-      </c>
-      <c r="B102" t="s">
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>37</v>
+      </c>
+      <c r="B104" t="s">
         <v>28</v>
       </c>
-      <c r="C102" s="2"/>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>83</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B105" t="s">
         <v>100</v>
       </c>
-      <c r="C103" s="2"/>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>45</v>
-      </c>
-      <c r="B104" t="s">
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" t="s">
         <v>80</v>
       </c>
-      <c r="C104" s="2"/>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>45</v>
-      </c>
-      <c r="B105" t="s">
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>45</v>
+      </c>
+      <c r="B107" t="s">
         <v>101</v>
       </c>
-      <c r="C105" s="2"/>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>45</v>
-      </c>
-      <c r="B106" t="s">
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" t="s">
         <v>81</v>
       </c>
-      <c r="C106" s="2"/>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>37</v>
-      </c>
-      <c r="B107" t="s">
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>37</v>
+      </c>
+      <c r="B109" t="s">
         <v>29</v>
       </c>
-      <c r="C107" s="2"/>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>45</v>
-      </c>
-      <c r="B108" t="s">
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>45</v>
+      </c>
+      <c r="B110" t="s">
         <v>29</v>
       </c>
-      <c r="C108" s="2"/>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>45</v>
-      </c>
-      <c r="B109" t="s">
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" t="s">
         <v>30</v>
       </c>
-      <c r="C109" s="2"/>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>37</v>
-      </c>
-      <c r="B110" t="s">
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>37</v>
+      </c>
+      <c r="B112" t="s">
         <v>30</v>
       </c>
-      <c r="C110" s="2"/>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>37</v>
-      </c>
-      <c r="B111" t="s">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>37</v>
+      </c>
+      <c r="B113" t="s">
         <v>96</v>
       </c>
-      <c r="C111" s="2"/>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>37</v>
-      </c>
-      <c r="B112" t="s">
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>37</v>
+      </c>
+      <c r="B114" t="s">
         <v>97</v>
       </c>
-      <c r="C112" s="2"/>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>45</v>
-      </c>
-      <c r="B113" t="s">
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>45</v>
+      </c>
+      <c r="B115" t="s">
         <v>31</v>
       </c>
-      <c r="C113" s="2"/>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>37</v>
-      </c>
-      <c r="B114" t="s">
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>37</v>
+      </c>
+      <c r="B116" t="s">
         <v>31</v>
       </c>
-      <c r="C114" s="2"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>37</v>
-      </c>
-      <c r="B115" t="s">
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>37</v>
+      </c>
+      <c r="B117" t="s">
         <v>32</v>
       </c>
-      <c r="C115" s="2"/>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>46</v>
-      </c>
-      <c r="B116" t="s">
-        <v>47</v>
-      </c>
-      <c r="C116" s="2"/>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>83</v>
-      </c>
-      <c r="B117" t="s">
-        <v>102</v>
-      </c>
-      <c r="C117" s="2"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>46</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
-      </c>
-      <c r="C118" s="2"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="D118" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B119" t="s">
-        <v>110</v>
-      </c>
-      <c r="C119" s="2"/>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>83</v>
       </c>
       <c r="B120" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>46</v>
+      </c>
+      <c r="B121" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>37</v>
+      </c>
+      <c r="B122" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>83</v>
+      </c>
+      <c r="B123" t="s">
         <v>82</v>
       </c>
-      <c r="C120" s="2"/>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>37</v>
-      </c>
-      <c r="B121" t="s">
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>37</v>
+      </c>
+      <c r="B124" t="s">
         <v>33</v>
       </c>
-      <c r="C121" s="2"/>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>37</v>
-      </c>
-      <c r="B122" t="s">
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>37</v>
+      </c>
+      <c r="B125" t="s">
         <v>34</v>
       </c>
-      <c r="C122" s="2"/>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>45</v>
-      </c>
-      <c r="B123" t="s">
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>45</v>
+      </c>
+      <c r="B126" t="s">
         <v>34</v>
       </c>
-      <c r="C123" s="2"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>37</v>
-      </c>
-      <c r="B124" t="s">
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>37</v>
+      </c>
+      <c r="B127" t="s">
         <v>35</v>
       </c>
-      <c r="C124" s="2"/>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>45</v>
-      </c>
-      <c r="B125" t="s">
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>45</v>
+      </c>
+      <c r="B128" t="s">
         <v>103</v>
       </c>
-      <c r="C125" s="2"/>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>37</v>
-      </c>
-      <c r="B126" t="s">
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129" t="s">
         <v>103</v>
       </c>
-      <c r="C126" s="2"/>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>37</v>
-      </c>
-      <c r="B127" t="s">
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>37</v>
+      </c>
+      <c r="B130" t="s">
         <v>109</v>
       </c>
-      <c r="C127" s="2"/>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>45</v>
-      </c>
-      <c r="B128" t="s">
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>45</v>
+      </c>
+      <c r="B131" t="s">
         <v>109</v>
       </c>
-      <c r="C128" s="2"/>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>37</v>
-      </c>
-      <c r="B129" t="s">
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>37</v>
+      </c>
+      <c r="B132" t="s">
         <v>36</v>
       </c>
-      <c r="C129" s="2"/>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>45</v>
-      </c>
-      <c r="B130" t="s">
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>45</v>
+      </c>
+      <c r="B133" t="s">
         <v>36</v>
       </c>
-      <c r="C130" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C130" xr:uid="{DBFEA6B2-9D01-4B24-AA77-47F03E8B424F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C130">
-      <sortCondition ref="B1:B130"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2630,7 +3690,7 @@
         <v>52</v>
       </c>
       <c r="C5" s="3">
-        <v>4.7941263282172374E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2674,7 +3734,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="3">
-        <v>5.001934235976787E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -2940,7 +4000,7 @@
         <v>52</v>
       </c>
       <c r="C5" s="3">
-        <v>4.7941263282172374E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2984,7 +4044,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="3">
-        <v>5.001934235976787E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -3010,7 +4070,15 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="1"/>
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.9820293494467551E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" s="1"/>

--- a/config/sla_targets.xlsx
+++ b/config/sla_targets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P.acquahrockson\Desktop\Sla-tracker\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2262F9DE-E63E-44C3-9666-CE90733EE14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D174852-CA7B-400B-9C6F-FD9B768D660B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="SMB" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Corporate!$A$1:$H$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Retail!$A$1:$H$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="81">
   <si>
     <t>Name</t>
   </si>
@@ -156,6 +157,132 @@
   </si>
   <si>
     <t>BENBOABEN PLUS LIMITED COMPANY</t>
+  </si>
+  <si>
+    <t>Top Connect Limited</t>
+  </si>
+  <si>
+    <t>Remittance</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>ASANTE KOTOKO SPORTING CLUB LIMITED</t>
+  </si>
+  <si>
+    <t>AYATICKETS LTD.</t>
+  </si>
+  <si>
+    <t>BLUE IDEAR</t>
+  </si>
+  <si>
+    <t>Chatbots Ghana</t>
+  </si>
+  <si>
+    <t>DEVPLUSE TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>Empowerment Worship Center</t>
+  </si>
+  <si>
+    <t>FAITHWORD CHARISMATIC MINISTRIES</t>
+  </si>
+  <si>
+    <t>Ga Rural Bank Limited</t>
+  </si>
+  <si>
+    <t>Group of pages Limited Company</t>
+  </si>
+  <si>
+    <t>Hyper Pay Ghana</t>
+  </si>
+  <si>
+    <t>IGNITIA GHANA LTD</t>
+  </si>
+  <si>
+    <t>INGAME TECHNOLOGY LTD</t>
+  </si>
+  <si>
+    <t>INTERZEN MICROFINANCE LIMITED</t>
+  </si>
+  <si>
+    <t>Jesi Education Technology Ltd.</t>
+  </si>
+  <si>
+    <t>KORBA PAY</t>
+  </si>
+  <si>
+    <t>Kwami Alone Enterprise</t>
+  </si>
+  <si>
+    <t>LUCKYLIVE (FORTULIVE)</t>
+  </si>
+  <si>
+    <t>Loud Company Limited</t>
+  </si>
+  <si>
+    <t>Mighty Service Venture</t>
+  </si>
+  <si>
+    <t>Mobicom Excite</t>
+  </si>
+  <si>
+    <t>POLICE HOSPITAL CO-OPERATIVE CREDIT UNION</t>
+  </si>
+  <si>
+    <t>PRESTO SOLUTIONS</t>
+  </si>
+  <si>
+    <t>Prudential Life</t>
+  </si>
+  <si>
+    <t>ROBSAM TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>SAVEST TECHNOLOGY LIMITED</t>
+  </si>
+  <si>
+    <t>STASH UP SUSU ENTERPRISE</t>
+  </si>
+  <si>
+    <t>Rancard Solutions</t>
+  </si>
+  <si>
+    <t>Speakupp Digital Services</t>
+  </si>
+  <si>
+    <t>Sunflower</t>
+  </si>
+  <si>
+    <t>TOP MENSAH VENTURES</t>
+  </si>
+  <si>
+    <t>UGCCU</t>
+  </si>
+  <si>
+    <t>VICTORY BIBLE CHURCH INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>WINWIN GAMES</t>
+  </si>
+  <si>
+    <t>WIWI GAMING AND ENTERTAINMENT LIMITED</t>
+  </si>
+  <si>
+    <t>EBONY OIL AND GAS LIMITED</t>
+  </si>
+  <si>
+    <t>ENTERPRISE CLAIMS</t>
+  </si>
+  <si>
+    <t>ENTERPRISE FUNERAL SERVICES GHANA LIMITED</t>
+  </si>
+  <si>
+    <t>Hydro Co-operative Credit Union</t>
+  </si>
+  <si>
+    <t>KRISH TECH ENTERPRISE</t>
   </si>
 </sst>
 </file>
@@ -197,7 +324,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -229,12 +356,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -267,7 +414,21 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -549,11 +710,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368F54FD-ED78-4E4A-BD37-CDE3D203AAB7}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultColWidth="25.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.6328125" customWidth="1"/>
+    <col min="2" max="2" width="45.90625" customWidth="1"/>
     <col min="3" max="3" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.36328125" bestFit="1" customWidth="1"/>
@@ -1105,6 +1266,2150 @@
         <v>1</v>
       </c>
       <c r="H21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="16">
+        <v>0</v>
+      </c>
+      <c r="E22" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F22" s="13">
+        <v>6</v>
+      </c>
+      <c r="G22" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="16">
+        <v>0</v>
+      </c>
+      <c r="E23" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F23" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="G23" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="16">
+        <v>0</v>
+      </c>
+      <c r="E24" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F24" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G24" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="16">
+        <v>0</v>
+      </c>
+      <c r="E25" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F25" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G25" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="16">
+        <v>0</v>
+      </c>
+      <c r="E26" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F26" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G26" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="16">
+        <v>1</v>
+      </c>
+      <c r="E27" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F27" s="13">
+        <v>1</v>
+      </c>
+      <c r="G27" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="16">
+        <v>51</v>
+      </c>
+      <c r="E28" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F28" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G28" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="16">
+        <v>101</v>
+      </c>
+      <c r="E29" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F29" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G29" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E30" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F30" s="13">
+        <v>30</v>
+      </c>
+      <c r="G30" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="16">
+        <v>1</v>
+      </c>
+      <c r="E31" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F31" s="13">
+        <v>1</v>
+      </c>
+      <c r="G31" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="16">
+        <v>101</v>
+      </c>
+      <c r="E32" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F32" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G32" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E33" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F33" s="13">
+        <v>20</v>
+      </c>
+      <c r="G33" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="16">
+        <v>1</v>
+      </c>
+      <c r="E34" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F34" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G34" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="16">
+        <v>1</v>
+      </c>
+      <c r="E35" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F35" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="16">
+        <v>1</v>
+      </c>
+      <c r="E36" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F36" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="16">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F37" s="13">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="G37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="16">
+        <v>1</v>
+      </c>
+      <c r="E38" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F38" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="16">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F39" s="13">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G39" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="16">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F40" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G40" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="16">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F41" s="13">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G41" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="16">
+        <v>1</v>
+      </c>
+      <c r="E42" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F42" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G42" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="16">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F43" s="13">
+        <v>1</v>
+      </c>
+      <c r="G43" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="16">
+        <v>51</v>
+      </c>
+      <c r="E44" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F44" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G44" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="16">
+        <v>101</v>
+      </c>
+      <c r="E45" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F45" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G45" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E46" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F46" s="13">
+        <v>30</v>
+      </c>
+      <c r="G46" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="16">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F47" s="13">
+        <v>1</v>
+      </c>
+      <c r="G47" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="16">
+        <v>101</v>
+      </c>
+      <c r="E48" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F48" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G48" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E49" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F49" s="13">
+        <v>20</v>
+      </c>
+      <c r="G49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="16">
+        <v>1</v>
+      </c>
+      <c r="E50" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F50" s="13">
+        <v>20</v>
+      </c>
+      <c r="G50" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="16">
+        <v>1</v>
+      </c>
+      <c r="E51" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F51" s="13">
+        <v>1</v>
+      </c>
+      <c r="G51" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="16">
+        <v>51</v>
+      </c>
+      <c r="E52" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F52" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G52" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="16">
+        <v>101</v>
+      </c>
+      <c r="E53" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F53" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G53" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E54" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F54" s="13">
+        <v>30</v>
+      </c>
+      <c r="G54" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="16">
+        <v>1</v>
+      </c>
+      <c r="E55" s="16">
+        <v>1000.99</v>
+      </c>
+      <c r="F55" s="13">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="G55" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="16">
+        <v>1</v>
+      </c>
+      <c r="E56" s="16">
+        <v>1000.99</v>
+      </c>
+      <c r="F56" s="13">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="G56" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" s="16">
+        <v>1001</v>
+      </c>
+      <c r="E57" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F57" s="13">
+        <v>10</v>
+      </c>
+      <c r="G57" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="16">
+        <v>1</v>
+      </c>
+      <c r="E58" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F58" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G58" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="16">
+        <v>1</v>
+      </c>
+      <c r="E59" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F59" s="13">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G59" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="16">
+        <v>1</v>
+      </c>
+      <c r="E60" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F60" s="13">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G60" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="16">
+        <v>1</v>
+      </c>
+      <c r="E61" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F61" s="13">
+        <v>1</v>
+      </c>
+      <c r="G61" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="16">
+        <v>51</v>
+      </c>
+      <c r="E62" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F62" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G62" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="16">
+        <v>101</v>
+      </c>
+      <c r="E63" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F63" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G63" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E64" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F64" s="13">
+        <v>30</v>
+      </c>
+      <c r="G64" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" s="16">
+        <v>1</v>
+      </c>
+      <c r="E65" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F65" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="16">
+        <v>51</v>
+      </c>
+      <c r="E66" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F66" s="13">
+        <v>1</v>
+      </c>
+      <c r="G66" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" s="16">
+        <v>101</v>
+      </c>
+      <c r="E67" s="16">
+        <v>1000.99</v>
+      </c>
+      <c r="F67" s="13">
+        <v>3</v>
+      </c>
+      <c r="G67" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" s="16">
+        <v>1001</v>
+      </c>
+      <c r="E68" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F68" s="13">
+        <v>5</v>
+      </c>
+      <c r="G68" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E69" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F69" s="13">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G69" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A70" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="16">
+        <v>1</v>
+      </c>
+      <c r="E70" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F70" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G70" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A71" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="16">
+        <v>1</v>
+      </c>
+      <c r="E71" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F71" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G71" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A72" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="16">
+        <v>1</v>
+      </c>
+      <c r="E72" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F72" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G72" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A73" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="16">
+        <v>1</v>
+      </c>
+      <c r="E73" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F73" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G73" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A74" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="16">
+        <v>1</v>
+      </c>
+      <c r="E74" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F74" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G74" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A75" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="16">
+        <v>1</v>
+      </c>
+      <c r="E75" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F75" s="13">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G75" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A76" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="16">
+        <v>1</v>
+      </c>
+      <c r="E76" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F76" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G76" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A77" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="16">
+        <v>1</v>
+      </c>
+      <c r="E77" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F77" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G77" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A78" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" s="16">
+        <v>1</v>
+      </c>
+      <c r="E78" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F78" s="13">
+        <v>1</v>
+      </c>
+      <c r="G78" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A79" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D79" s="16">
+        <v>51</v>
+      </c>
+      <c r="E79" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F79" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G79" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A80" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" s="16">
+        <v>101</v>
+      </c>
+      <c r="E80" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F80" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G80" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D81" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E81" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F81" s="13">
+        <v>30</v>
+      </c>
+      <c r="G81" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="16">
+        <v>1</v>
+      </c>
+      <c r="E82" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F82" s="13">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="G82" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" s="16">
+        <v>1</v>
+      </c>
+      <c r="E83" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F83" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G83" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="16">
+        <v>1</v>
+      </c>
+      <c r="E84" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F84" s="13">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="G84" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="16">
+        <v>1</v>
+      </c>
+      <c r="E85" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F85" s="13">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="G85" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D86" s="16">
+        <v>1</v>
+      </c>
+      <c r="E86" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F86" s="13">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G86" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" s="16">
+        <v>1</v>
+      </c>
+      <c r="E87" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F87" s="13">
+        <v>1</v>
+      </c>
+      <c r="G87" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="16">
+        <v>1</v>
+      </c>
+      <c r="E88" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F88" s="13">
+        <f>2%</f>
+        <v>0.02</v>
+      </c>
+      <c r="G88" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D89" s="16">
+        <v>1</v>
+      </c>
+      <c r="E89" s="16">
+        <v>1000.99</v>
+      </c>
+      <c r="F89" s="13">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G89" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" s="16">
+        <v>1</v>
+      </c>
+      <c r="E90" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F90" s="13">
+        <v>1</v>
+      </c>
+      <c r="G90" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="16">
+        <v>1</v>
+      </c>
+      <c r="E91" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F91" s="13">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G91" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="16">
+        <v>1</v>
+      </c>
+      <c r="E92" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F92" s="13">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G92" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="16">
+        <v>1</v>
+      </c>
+      <c r="E93" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F93" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="G93" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" s="16">
+        <v>1</v>
+      </c>
+      <c r="E94" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F94" s="13">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G94" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" s="16">
+        <v>1</v>
+      </c>
+      <c r="E95" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F95" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G95" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>4</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C96" t="s">
+        <v>36</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>999999</v>
+      </c>
+      <c r="F96" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
+      <c r="H96" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C97" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>999999</v>
+      </c>
+      <c r="F97" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>4</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="16">
+        <v>1</v>
+      </c>
+      <c r="E98" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F98" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G98" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H98" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="16">
+        <v>1</v>
+      </c>
+      <c r="E99" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F99" s="13">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G99" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D100" s="16">
+        <v>1</v>
+      </c>
+      <c r="E100" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F100" s="13">
+        <f>0.3%</f>
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G100" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D101" s="16">
+        <v>1</v>
+      </c>
+      <c r="E101" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F101" s="13">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G101" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>4</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102" s="16">
+        <v>20001</v>
+      </c>
+      <c r="E102" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F102" s="13">
+        <v>10</v>
+      </c>
+      <c r="G102" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>4</v>
+      </c>
+      <c r="B103" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C103" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>999999</v>
+      </c>
+      <c r="F103" s="13">
+        <v>0</v>
+      </c>
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1259,7 +3564,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="14" t="s">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1441,7 +3746,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="14" t="s">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1571,7 +3876,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="14" t="s">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1701,7 +4006,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="14" t="s">
+      <c r="A23" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="1" t="s">

--- a/config/sla_targets.xlsx
+++ b/config/sla_targets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P.acquahrockson\Desktop\Sla-tracker\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D174852-CA7B-400B-9C6F-FD9B768D660B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD1024E-BAA3-4785-B920-0135BE53DA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="SMB" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Corporate!$A$1:$H$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Corporate!$A$1:$H$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Retail!$A$1:$H$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="84">
   <si>
     <t>Name</t>
   </si>
@@ -283,6 +283,15 @@
   </si>
   <si>
     <t>KRISH TECH ENTERPRISE</t>
+  </si>
+  <si>
+    <t>E-Distribution</t>
+  </si>
+  <si>
+    <t>Omni Group Ghana ltd</t>
+  </si>
+  <si>
+    <t>Loyalty Insurance Disbursement</t>
   </si>
 </sst>
 </file>
@@ -381,7 +390,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -428,6 +437,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -710,17 +743,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368F54FD-ED78-4E4A-BD37-CDE3D203AAB7}">
-  <dimension ref="A1:H103"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr defaultColWidth="25.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.90625" customWidth="1"/>
-    <col min="3" max="3" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.81640625" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -749,7 +783,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -775,59 +809,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>38</v>
+      <c r="B3" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="6">
-        <v>50.99</v>
-      </c>
-      <c r="F3" s="12">
-        <v>1</v>
+        <v>999999</v>
+      </c>
+      <c r="F3" s="23">
+        <v>0.05</v>
       </c>
       <c r="G3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>38</v>
+      <c r="B4" s="21" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="6">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E4" s="6">
-        <v>100.99</v>
-      </c>
-      <c r="F4" s="12">
-        <v>1.5</v>
+        <v>999999</v>
+      </c>
+      <c r="F4" s="23">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -838,22 +872,22 @@
         <v>35</v>
       </c>
       <c r="D5" s="6">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6">
-        <v>2000.99</v>
+        <v>50.99</v>
       </c>
       <c r="F5" s="12">
-        <v>1.4999999999999999E-2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
@@ -861,27 +895,27 @@
         <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="6">
-        <v>2001</v>
+        <v>51</v>
       </c>
       <c r="E6" s="6">
-        <v>999999</v>
+        <v>100.99</v>
       </c>
       <c r="F6" s="12">
-        <v>1.4999999999999999E-2</v>
+        <v>1.5</v>
       </c>
       <c r="G6" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>38</v>
@@ -890,48 +924,48 @@
         <v>35</v>
       </c>
       <c r="D7" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="E7" s="6">
-        <v>50.99</v>
+        <v>2000.99</v>
       </c>
       <c r="F7" s="12">
-        <v>1</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G7" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="6">
-        <v>51</v>
+        <v>2001</v>
       </c>
       <c r="E8" s="6">
-        <v>100.99</v>
+        <v>999999</v>
       </c>
       <c r="F8" s="12">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G8" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H8" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -942,22 +976,22 @@
         <v>35</v>
       </c>
       <c r="D9" s="6">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6">
-        <v>2000.99</v>
+        <v>50.99</v>
       </c>
       <c r="F9" s="12">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="G9" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
@@ -965,160 +999,160 @@
         <v>38</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="6">
-        <v>2001</v>
+        <v>51</v>
       </c>
       <c r="E10" s="6">
-        <v>999999</v>
+        <v>100.99</v>
       </c>
       <c r="F10" s="12">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="G10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D11" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="E11" s="6">
-        <v>50.99</v>
+        <v>2000.99</v>
       </c>
       <c r="F11" s="12">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="G11" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="6">
-        <v>51</v>
+        <v>2001</v>
       </c>
       <c r="E12" s="6">
-        <v>100.99</v>
+        <v>999999</v>
       </c>
       <c r="F12" s="12">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="G12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="6">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="E13" s="6">
-        <v>1000.99</v>
+        <v>999999</v>
       </c>
       <c r="F13" s="12">
-        <v>3</v>
+        <v>0.01</v>
       </c>
       <c r="G13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>44</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="E14" s="6">
-        <v>2000.99</v>
-      </c>
-      <c r="F14" s="12">
-        <v>0.05</v>
+        <v>999999</v>
+      </c>
+      <c r="F14" s="23">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G14" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H14" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" s="6">
-        <v>2001</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6">
         <v>999999</v>
       </c>
-      <c r="F15" s="12">
-        <v>0.05</v>
+      <c r="F15" s="23">
+        <v>0.02</v>
       </c>
       <c r="G15" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H15" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H15" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>26</v>
+      <c r="B16" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>35</v>
@@ -1129,22 +1163,22 @@
       <c r="E16" s="6">
         <v>50.99</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="23">
         <v>1</v>
       </c>
       <c r="G16" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H16" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>26</v>
+      <c r="B17" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>35</v>
@@ -1155,22 +1189,22 @@
       <c r="E17" s="6">
         <v>100.99</v>
       </c>
-      <c r="F17" s="12">
-        <v>1</v>
+      <c r="F17" s="23">
+        <v>1.5</v>
       </c>
       <c r="G17" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="H17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H17" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>26</v>
+      <c r="B18" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>35</v>
@@ -1181,22 +1215,22 @@
       <c r="E18" s="6">
         <v>2000.99</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="23">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G18" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H18" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H18" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>26</v>
+      <c r="B19" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>36</v>
@@ -1207,165 +1241,166 @@
       <c r="E19" s="6">
         <v>999999</v>
       </c>
-      <c r="F19" s="12">
-        <v>1.4999999999999999E-2</v>
+      <c r="F19" s="23">
+        <v>30</v>
       </c>
       <c r="G19" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="26">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>2</v>
+      <c r="B20" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="6">
-        <v>999999</v>
-      </c>
-      <c r="F20" s="12">
-        <v>5.0000000000000001E-3</v>
+        <v>100.99</v>
+      </c>
+      <c r="F20" s="23">
+        <v>1</v>
       </c>
       <c r="G20" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>23</v>
+      <c r="B21" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" s="6">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="E21" s="6">
-        <v>999999</v>
-      </c>
-      <c r="F21" s="12">
-        <v>0</v>
+        <v>2000.99</v>
+      </c>
+      <c r="F21" s="23">
+        <v>0.01</v>
       </c>
       <c r="G21" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H21" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D22" s="16">
-        <v>0</v>
+        <v>2001</v>
       </c>
       <c r="E22" s="16">
         <v>999999</v>
       </c>
       <c r="F22" s="13">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G22" s="17" t="b">
         <v>0</v>
       </c>
       <c r="H22" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" s="16">
         <v>0</v>
       </c>
       <c r="E23" s="16">
-        <v>999999</v>
+        <v>50.99</v>
       </c>
       <c r="F23" s="13">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="G23" s="17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" s="16">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E24" s="16">
-        <v>999999</v>
+        <v>100.99</v>
       </c>
       <c r="F24" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="16">
+        <v>101</v>
+      </c>
+      <c r="E25" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F25" s="13">
+        <f>1.5%</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G24" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="16">
-        <v>0</v>
-      </c>
-      <c r="E25" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F25" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
       <c r="G25" s="17" t="b">
         <v>1</v>
       </c>
@@ -1373,35 +1408,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" s="16">
-        <v>0</v>
+        <v>2001</v>
       </c>
       <c r="E26" s="16">
         <v>999999</v>
       </c>
       <c r="F26" s="13">
-        <v>0.02</v>
+        <v>30</v>
       </c>
       <c r="G26" s="17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="15" t="s">
-        <v>3</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>46</v>
@@ -1410,10 +1445,10 @@
         <v>35</v>
       </c>
       <c r="D27" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="16">
-        <v>50.99</v>
+        <v>100.99</v>
       </c>
       <c r="F27" s="13">
         <v>1</v>
@@ -1425,9 +1460,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="15" t="s">
-        <v>3</v>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>46</v>
@@ -1436,178 +1471,181 @@
         <v>35</v>
       </c>
       <c r="D28" s="16">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="E28" s="16">
-        <v>100.99</v>
+        <v>2000.99</v>
       </c>
       <c r="F28" s="13">
         <v>1.5</v>
       </c>
       <c r="G28" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="15" t="s">
-        <v>3</v>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D29" s="16">
-        <v>101</v>
+        <v>2001</v>
       </c>
       <c r="E29" s="16">
-        <v>2000.99</v>
+        <v>999999</v>
       </c>
       <c r="F29" s="13">
-        <v>1.4999999999999999E-2</v>
+        <v>20</v>
       </c>
       <c r="G29" s="17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D30" s="16">
-        <v>2001</v>
+        <v>1</v>
       </c>
       <c r="E30" s="16">
         <v>999999</v>
       </c>
       <c r="F30" s="13">
-        <v>30</v>
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G30" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" s="16">
         <v>1</v>
       </c>
       <c r="E31" s="16">
-        <v>100.99</v>
+        <v>999999</v>
       </c>
       <c r="F31" s="13">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="G31" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D32" s="16">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="E32" s="16">
-        <v>2000.99</v>
+        <v>999999</v>
       </c>
       <c r="F32" s="13">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="G32" s="17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="16">
+        <v>1</v>
+      </c>
+      <c r="E33" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F33" s="13">
+        <f>2%</f>
+        <v>0.02</v>
+      </c>
+      <c r="G33" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="15" t="s">
+      <c r="B34" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="16">
-        <v>2001</v>
-      </c>
-      <c r="E33" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F33" s="13">
-        <v>20</v>
-      </c>
-      <c r="G33" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>34</v>
-      </c>
       <c r="D34" s="16">
         <v>1</v>
       </c>
       <c r="E34" s="16">
-        <v>999999</v>
+        <v>1000.99</v>
       </c>
       <c r="F34" s="13">
-        <v>0.02</v>
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G34" s="17" t="b">
         <v>1</v>
       </c>
       <c r="H34" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
         <v>3</v>
       </c>
@@ -1633,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
         <v>3</v>
       </c>
@@ -1644,7 +1682,7 @@
         <v>34</v>
       </c>
       <c r="D36" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="16">
         <v>999999</v>
@@ -1659,246 +1697,247 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B37" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="16">
+        <v>0</v>
+      </c>
+      <c r="E37" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F37" s="13">
+        <v>1</v>
+      </c>
+      <c r="G37" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="19">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19">
+        <v>999999</v>
+      </c>
+      <c r="F38" s="13">
+        <f>17.22%</f>
+        <v>0.17219999999999999</v>
+      </c>
+      <c r="G38" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="16">
-        <v>1</v>
-      </c>
-      <c r="E37" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F37" s="13">
+      <c r="C39" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" s="16">
+        <v>0</v>
+      </c>
+      <c r="E39" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F39" s="24">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G39" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="16">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F40" s="13">
         <v>1.8499999999999999E-2</v>
       </c>
-      <c r="G37" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="16">
-        <v>1</v>
-      </c>
-      <c r="E38" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F38" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G38" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="14" t="s">
+      <c r="G40" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="16">
+        <v>0</v>
+      </c>
+      <c r="E41" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F41" s="24">
+        <v>0</v>
+      </c>
+      <c r="G41" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="16">
+        <v>1</v>
+      </c>
+      <c r="E42" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F42" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="16">
         <v>51</v>
       </c>
-      <c r="C39" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D39" s="16">
-        <v>1</v>
-      </c>
-      <c r="E39" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F39" s="13">
-        <v>1.2E-2</v>
-      </c>
-      <c r="G39" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D40" s="16">
-        <v>1</v>
-      </c>
-      <c r="E40" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F40" s="13">
-        <v>0.01</v>
-      </c>
-      <c r="G40" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="16">
-        <v>1</v>
-      </c>
-      <c r="E41" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F41" s="13">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G41" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="16">
-        <v>1</v>
-      </c>
-      <c r="E42" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F42" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G42" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" s="16">
-        <v>1</v>
-      </c>
       <c r="E43" s="16">
-        <v>50.99</v>
-      </c>
-      <c r="F43" s="13">
+        <v>100.99</v>
+      </c>
+      <c r="F43" s="24">
         <v>1</v>
       </c>
       <c r="G43" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="H43" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H43" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>24</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D44" s="16">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="E44" s="16">
-        <v>100.99</v>
-      </c>
-      <c r="F44" s="13">
-        <v>1.5</v>
+        <v>1000.99</v>
+      </c>
+      <c r="F44" s="24">
+        <v>3</v>
       </c>
       <c r="G44" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="H44" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H44" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>24</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D45" s="16">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="E45" s="16">
         <v>2000.99</v>
       </c>
-      <c r="F45" s="13">
-        <v>1.4999999999999999E-2</v>
+      <c r="F45" s="24">
+        <v>0.05</v>
       </c>
       <c r="G45" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="H45" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H45" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>24</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>36</v>
@@ -1909,243 +1948,245 @@
       <c r="E46" s="16">
         <v>999999</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="24">
+        <v>0.05</v>
+      </c>
+      <c r="G46" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="16">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F47" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G47" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="16">
+        <v>1</v>
+      </c>
+      <c r="E48" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F48" s="24">
+        <v>1</v>
+      </c>
+      <c r="G48" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="16">
+        <v>51</v>
+      </c>
+      <c r="E49" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F49" s="24">
+        <v>1</v>
+      </c>
+      <c r="G49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="16">
+        <v>101</v>
+      </c>
+      <c r="E50" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F50" s="24">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G50" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E51" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F51" s="24">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G51" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="28">
         <v>30</v>
       </c>
-      <c r="G46" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="15" t="s">
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="16">
+        <v>1</v>
+      </c>
+      <c r="E52" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F52" s="13">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G52" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D47" s="16">
-        <v>1</v>
-      </c>
-      <c r="E47" s="16">
-        <v>100.99</v>
-      </c>
-      <c r="F47" s="13">
-        <v>1</v>
-      </c>
-      <c r="G47" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D48" s="16">
-        <v>101</v>
-      </c>
-      <c r="E48" s="16">
-        <v>2000.99</v>
-      </c>
-      <c r="F48" s="13">
+      <c r="B53" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="16">
+        <v>1</v>
+      </c>
+      <c r="E53" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F53" s="13">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G53" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="16">
+        <v>1</v>
+      </c>
+      <c r="E54" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F54" s="13">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G54" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H54" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="16">
+        <v>1</v>
+      </c>
+      <c r="E55" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F55" s="13">
         <v>0.01</v>
       </c>
-      <c r="G48" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" s="16">
-        <v>2001</v>
-      </c>
-      <c r="E49" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F49" s="13">
-        <v>20</v>
-      </c>
-      <c r="G49" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50" s="16">
-        <v>1</v>
-      </c>
-      <c r="E50" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F50" s="13">
-        <v>20</v>
-      </c>
-      <c r="G50" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D51" s="16">
-        <v>1</v>
-      </c>
-      <c r="E51" s="16">
-        <v>50.99</v>
-      </c>
-      <c r="F51" s="13">
-        <v>1</v>
-      </c>
-      <c r="G51" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D52" s="16">
-        <v>51</v>
-      </c>
-      <c r="E52" s="16">
-        <v>100.99</v>
-      </c>
-      <c r="F52" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="G52" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H52" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D53" s="16">
-        <v>101</v>
-      </c>
-      <c r="E53" s="16">
-        <v>2000.99</v>
-      </c>
-      <c r="F53" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G53" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B54" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D54" s="16">
-        <v>2001</v>
-      </c>
-      <c r="E54" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F54" s="13">
-        <v>30</v>
-      </c>
-      <c r="G54" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D55" s="16">
-        <v>1</v>
-      </c>
-      <c r="E55" s="16">
-        <v>1000.99</v>
-      </c>
-      <c r="F55" s="13">
-        <v>1.8499999999999999E-2</v>
-      </c>
       <c r="G55" s="17" t="b">
         <v>1</v>
       </c>
@@ -2153,24 +2194,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D56" s="16">
         <v>1</v>
       </c>
       <c r="E56" s="16">
-        <v>1000.99</v>
+        <v>999999</v>
       </c>
       <c r="F56" s="13">
-        <v>1.8499999999999999E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G56" s="17" t="b">
         <v>1</v>
@@ -2179,1176 +2220,1173 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="15" t="s">
         <v>4</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C57" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="16">
+        <v>1</v>
+      </c>
+      <c r="E57" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F57" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="G57" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="16">
+        <v>1</v>
+      </c>
+      <c r="E58" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F58" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G58" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="16">
+        <v>1</v>
+      </c>
+      <c r="E59" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F59" s="13">
+        <v>1</v>
+      </c>
+      <c r="G59" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="16">
+        <v>51</v>
+      </c>
+      <c r="E60" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F60" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G60" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="16">
+        <v>101</v>
+      </c>
+      <c r="E61" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F61" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G61" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="16">
-        <v>1001</v>
-      </c>
-      <c r="E57" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F57" s="13">
-        <v>10</v>
-      </c>
-      <c r="G57" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="16">
-        <v>1</v>
-      </c>
-      <c r="E58" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F58" s="13">
-        <v>0.02</v>
-      </c>
-      <c r="G58" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" s="16">
-        <v>1</v>
-      </c>
-      <c r="E59" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F59" s="13">
+      <c r="D62" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E62" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F62" s="13">
+        <v>30</v>
+      </c>
+      <c r="G62" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="16">
+        <v>1</v>
+      </c>
+      <c r="E63" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F63" s="13">
+        <v>1</v>
+      </c>
+      <c r="G63" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64" s="16">
+        <v>101</v>
+      </c>
+      <c r="E64" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F64" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G64" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D65" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E65" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F65" s="13">
+        <v>20</v>
+      </c>
+      <c r="G65" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="16">
+        <v>1</v>
+      </c>
+      <c r="E66" s="16">
+        <v>2400</v>
+      </c>
+      <c r="F66" s="13">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="G66" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="16">
+        <v>1</v>
+      </c>
+      <c r="E67" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F67" s="13">
         <f>1.5%</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G59" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="16">
-        <v>1</v>
-      </c>
-      <c r="E60" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F60" s="13">
+      <c r="G67" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="16">
+        <v>1</v>
+      </c>
+      <c r="E68" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F68" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G68" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69" s="16">
+        <v>1</v>
+      </c>
+      <c r="E69" s="16">
+        <v>50.99</v>
+      </c>
+      <c r="F69" s="13">
+        <v>1</v>
+      </c>
+      <c r="G69" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" s="16">
+        <v>51</v>
+      </c>
+      <c r="E70" s="16">
+        <v>100.99</v>
+      </c>
+      <c r="F70" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G70" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71" s="16">
+        <v>101</v>
+      </c>
+      <c r="E71" s="16">
+        <v>2000.99</v>
+      </c>
+      <c r="F71" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G71" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72" s="16">
+        <v>2001</v>
+      </c>
+      <c r="E72" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F72" s="13">
+        <v>30</v>
+      </c>
+      <c r="G72" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="19">
+        <v>0</v>
+      </c>
+      <c r="E73" s="19">
+        <v>999999</v>
+      </c>
+      <c r="F73" s="13">
+        <f>6.27%</f>
+        <v>6.2699999999999992E-2</v>
+      </c>
+      <c r="G73" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="16">
+        <v>1</v>
+      </c>
+      <c r="E74" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F74" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G74" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D75" s="19">
+        <v>0</v>
+      </c>
+      <c r="E75" s="19">
+        <v>999999</v>
+      </c>
+      <c r="F75" s="13">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G75" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="10">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="16">
+        <v>1</v>
+      </c>
+      <c r="E76" s="16">
+        <v>1000.99</v>
+      </c>
+      <c r="F76" s="13">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="G76" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="16">
+        <v>1</v>
+      </c>
+      <c r="E77" s="16">
+        <v>1000.99</v>
+      </c>
+      <c r="F77" s="13">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="G77" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D78" s="16">
+        <v>1001</v>
+      </c>
+      <c r="E78" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F78" s="13">
+        <v>10</v>
+      </c>
+      <c r="G78" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="16">
+        <v>1</v>
+      </c>
+      <c r="E79" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F79" s="13">
         <f>1.5%</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G60" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="14" t="s">
+      <c r="G79" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" s="16">
+        <v>1</v>
+      </c>
+      <c r="E80" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F80" s="13">
+        <f>1.5%</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G80" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" s="19">
+        <v>0</v>
+      </c>
+      <c r="E81" s="19">
+        <v>999999</v>
+      </c>
+      <c r="F81" s="13">
+        <v>2</v>
+      </c>
+      <c r="G81" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="16">
-        <v>1</v>
-      </c>
-      <c r="E61" s="16">
+      <c r="C82" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D82" s="16">
+        <v>1</v>
+      </c>
+      <c r="E82" s="16">
         <v>50.99</v>
       </c>
-      <c r="F61" s="13">
-        <v>1</v>
-      </c>
-      <c r="G61" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="14" t="s">
+      <c r="F82" s="13">
+        <v>1</v>
+      </c>
+      <c r="G82" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D62" s="16">
+      <c r="C83" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D83" s="16">
         <v>51</v>
       </c>
-      <c r="E62" s="16">
+      <c r="E83" s="16">
         <v>100.99</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F83" s="13">
         <v>1.5</v>
       </c>
-      <c r="G62" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="14" t="s">
+      <c r="G83" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D63" s="16">
+      <c r="C84" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84" s="16">
         <v>101</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E84" s="16">
         <v>2000.99</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F84" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G63" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="14" t="s">
+      <c r="G84" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C85" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D85" s="16">
         <v>2001</v>
       </c>
-      <c r="E64" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F64" s="13">
+      <c r="E85" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F85" s="13">
         <v>30</v>
       </c>
-      <c r="G64" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64" s="10">
+      <c r="G85" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="15" t="s">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B86" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C65" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D65" s="16">
-        <v>1</v>
-      </c>
-      <c r="E65" s="16">
+      <c r="C86" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" s="16">
+        <v>1</v>
+      </c>
+      <c r="E86" s="16">
         <v>50.99</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F86" s="13">
         <v>0.5</v>
       </c>
-      <c r="G65" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H65" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="15" t="s">
+      <c r="G86" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B87" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C66" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D66" s="16">
+      <c r="C87" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D87" s="16">
         <v>51</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E87" s="16">
         <v>100.99</v>
       </c>
-      <c r="F66" s="13">
-        <v>1</v>
-      </c>
-      <c r="G66" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="15" t="s">
+      <c r="F87" s="13">
+        <v>1</v>
+      </c>
+      <c r="G87" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B88" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D67" s="16">
+      <c r="C88" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88" s="16">
         <v>101</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E88" s="16">
         <v>1000.99</v>
       </c>
-      <c r="F67" s="13">
-        <v>3</v>
-      </c>
-      <c r="G67" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H67" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="15" t="s">
+      <c r="F88" s="13">
+        <v>3</v>
+      </c>
+      <c r="G88" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B89" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D68" s="16">
+      <c r="C89" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" s="16">
         <v>1001</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E89" s="16">
         <v>2000.99</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F89" s="13">
         <v>5</v>
       </c>
-      <c r="G68" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68" s="10" t="s">
+      <c r="G89" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="15" t="s">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B90" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C90" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D69" s="16">
+      <c r="D90" s="16">
         <v>2001</v>
       </c>
-      <c r="E69" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F69" s="13">
+      <c r="E90" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F90" s="13">
         <f>0.5%</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G69" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H69" s="10">
+      <c r="G90" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="14" t="s">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D70" s="16">
-        <v>1</v>
-      </c>
-      <c r="E70" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F70" s="13">
+      <c r="C91" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="16">
+        <v>1</v>
+      </c>
+      <c r="E91" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F91" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G70" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="14" t="s">
+      <c r="G91" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" s="19">
+        <v>1</v>
+      </c>
+      <c r="E92" s="19">
+        <v>999999</v>
+      </c>
+      <c r="F92" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G92" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D71" s="16">
-        <v>1</v>
-      </c>
-      <c r="E71" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F71" s="13">
+      <c r="C93" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="16">
+        <v>1</v>
+      </c>
+      <c r="E93" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F93" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G71" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H71" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="14" t="s">
+      <c r="G93" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" s="16">
+        <v>1</v>
+      </c>
+      <c r="E94" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F94" s="13">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G94" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D72" s="16">
-        <v>1</v>
-      </c>
-      <c r="E72" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F72" s="13">
+      <c r="C95" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" s="16">
+        <v>0</v>
+      </c>
+      <c r="E95" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F95" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G72" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D73" s="16">
-        <v>1</v>
-      </c>
-      <c r="E73" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F73" s="13">
+      <c r="G95" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H95" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>999999</v>
+      </c>
+      <c r="F96" s="13">
+        <f>1.5%</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G73" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A74" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D74" s="16">
-        <v>1</v>
-      </c>
-      <c r="E74" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F74" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G74" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A75" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C75" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D75" s="16">
-        <v>1</v>
-      </c>
-      <c r="E75" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F75" s="13">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="G75" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H75" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A76" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D76" s="16">
-        <v>1</v>
-      </c>
-      <c r="E76" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F76" s="13">
-        <v>0.02</v>
-      </c>
-      <c r="G76" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A77" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D77" s="16">
-        <v>1</v>
-      </c>
-      <c r="E77" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F77" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G77" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A78" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C78" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D78" s="16">
-        <v>1</v>
-      </c>
-      <c r="E78" s="16">
-        <v>50.99</v>
-      </c>
-      <c r="F78" s="13">
-        <v>1</v>
-      </c>
-      <c r="G78" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A79" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D79" s="16">
-        <v>51</v>
-      </c>
-      <c r="E79" s="16">
-        <v>100.99</v>
-      </c>
-      <c r="F79" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="G79" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D80" s="16">
-        <v>101</v>
-      </c>
-      <c r="E80" s="16">
-        <v>2000.99</v>
-      </c>
-      <c r="F80" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G80" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C81" s="15" t="s">
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
+      <c r="H96" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C97" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D81" s="16">
-        <v>2001</v>
-      </c>
-      <c r="E81" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F81" s="13">
-        <v>30</v>
-      </c>
-      <c r="G81" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C82" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D82" s="16">
-        <v>1</v>
-      </c>
-      <c r="E82" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F82" s="13">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="G82" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C83" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D83" s="16">
-        <v>1</v>
-      </c>
-      <c r="E83" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F83" s="13">
-        <v>0.02</v>
-      </c>
-      <c r="G83" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D84" s="16">
-        <v>1</v>
-      </c>
-      <c r="E84" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F84" s="13">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="G84" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H84" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D85" s="16">
-        <v>1</v>
-      </c>
-      <c r="E85" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F85" s="13">
-        <v>1.8499999999999999E-2</v>
-      </c>
-      <c r="G85" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D86" s="16">
-        <v>1</v>
-      </c>
-      <c r="E86" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F86" s="13">
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>999999</v>
+      </c>
+      <c r="F97" s="13">
         <f>0.5%</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G86" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" s="15" t="s">
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" s="10">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="16">
+        <v>1</v>
+      </c>
+      <c r="E98" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F98" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G98" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H98" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B87" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C87" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D87" s="16">
-        <v>1</v>
-      </c>
-      <c r="E87" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F87" s="13">
-        <v>1</v>
-      </c>
-      <c r="G87" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A88" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D88" s="16">
-        <v>1</v>
-      </c>
-      <c r="E88" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F88" s="13">
-        <f>2%</f>
+      <c r="B99" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="19">
+        <v>1</v>
+      </c>
+      <c r="E99" s="19">
+        <v>999999</v>
+      </c>
+      <c r="F99" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G99" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D100" s="16">
+        <v>1</v>
+      </c>
+      <c r="E100" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F100" s="13">
         <v>0.02</v>
       </c>
-      <c r="G88" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H88" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" s="15" t="s">
+      <c r="G100" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B89" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C89" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D89" s="16">
-        <v>1</v>
-      </c>
-      <c r="E89" s="16">
-        <v>1000.99</v>
-      </c>
-      <c r="F89" s="13">
-        <f>0.5%</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G89" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H89" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" s="16">
-        <v>1</v>
-      </c>
-      <c r="E90" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F90" s="13">
-        <v>1</v>
-      </c>
-      <c r="G90" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C91" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D91" s="16">
-        <v>1</v>
-      </c>
-      <c r="E91" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F91" s="13">
-        <f>1.5%</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G91" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H91" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D92" s="16">
-        <v>1</v>
-      </c>
-      <c r="E92" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F92" s="13">
-        <f>1.5%</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G92" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H92" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A93" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D93" s="16">
-        <v>1</v>
-      </c>
-      <c r="E93" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F93" s="13">
-        <v>0.05</v>
-      </c>
-      <c r="G93" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A94" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D94" s="16">
-        <v>1</v>
-      </c>
-      <c r="E94" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F94" s="13">
-        <f>1.5%</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G94" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H94" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A95" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C95" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D95" s="16">
-        <v>1</v>
-      </c>
-      <c r="E95" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F95" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="G95" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>4</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C96" t="s">
-        <v>36</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="E96">
-        <v>999999</v>
-      </c>
-      <c r="F96" s="13">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G96" t="b">
-        <v>1</v>
-      </c>
-      <c r="H96" s="10">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>4</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C97" t="s">
-        <v>34</v>
-      </c>
-      <c r="D97">
-        <v>1</v>
-      </c>
-      <c r="E97">
-        <v>999999</v>
-      </c>
-      <c r="F97" s="13">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G97" t="b">
-        <v>1</v>
-      </c>
-      <c r="H97" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>4</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D98" s="16">
-        <v>1</v>
-      </c>
-      <c r="E98" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F98" s="13">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G98" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H98" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A99" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B99" s="14" t="s">
+      <c r="B101" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C99" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D99" s="16">
-        <v>1</v>
-      </c>
-      <c r="E99" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F99" s="13">
-        <f>0.5%</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G99" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H99" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A100" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C100" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D100" s="16">
-        <v>1</v>
-      </c>
-      <c r="E100" s="16">
-        <v>999999</v>
-      </c>
-      <c r="F100" s="13">
-        <f>0.3%</f>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G100" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>4</v>
-      </c>
-      <c r="B101" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="C101" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D101" s="16">
         <v>1</v>
       </c>
       <c r="E101" s="16">
-        <v>2000.99</v>
+        <v>999999</v>
       </c>
       <c r="F101" s="13">
         <f>0.5%</f>
@@ -3361,59 +3399,461 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>4</v>
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="20" t="s">
+        <v>3</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D102" s="16">
-        <v>20001</v>
+        <v>1</v>
       </c>
       <c r="E102" s="16">
         <v>999999</v>
       </c>
       <c r="F102" s="13">
-        <v>10</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G102" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>4</v>
       </c>
       <c r="B103" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103" s="22">
+        <v>1</v>
+      </c>
+      <c r="E103" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F103" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G103" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H103" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C104" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" s="22">
+        <v>1</v>
+      </c>
+      <c r="E104" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F104" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G104" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H104" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B105" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C105" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="22">
+        <v>0</v>
+      </c>
+      <c r="E105" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F105" s="13">
+        <v>6</v>
+      </c>
+      <c r="G105" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C106" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D106" s="22">
+        <v>1</v>
+      </c>
+      <c r="E106" s="22">
+        <v>50.99</v>
+      </c>
+      <c r="F106" s="13">
+        <v>1</v>
+      </c>
+      <c r="G106" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D107" s="22">
+        <v>51</v>
+      </c>
+      <c r="E107" s="22">
+        <v>100.99</v>
+      </c>
+      <c r="F107" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G107" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D108" s="22">
+        <v>101</v>
+      </c>
+      <c r="E108" s="22">
+        <v>2000.99</v>
+      </c>
+      <c r="F108" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G108" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H108" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C109" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D109" s="22">
+        <v>2001</v>
+      </c>
+      <c r="E109" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F109" s="13">
+        <v>30</v>
+      </c>
+      <c r="G109" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C110" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D110" s="22">
+        <v>1</v>
+      </c>
+      <c r="E110" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F110" s="13">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="G110" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H110" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B111" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D111" s="6">
+        <v>1</v>
+      </c>
+      <c r="E111" s="6">
+        <v>999999</v>
+      </c>
+      <c r="F111" s="23">
+        <f>0.3%</f>
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G111" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H111" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D112" s="22">
+        <v>1</v>
+      </c>
+      <c r="E112" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F112" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G112" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H112" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" s="22">
+        <v>1</v>
+      </c>
+      <c r="E113" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F113" s="13">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="G113" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H113" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D114" s="22">
+        <v>1</v>
+      </c>
+      <c r="E114" s="22">
+        <v>2000.99</v>
+      </c>
+      <c r="F114" s="13">
+        <f>0.5%</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G114" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H114" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>4</v>
+      </c>
+      <c r="B115" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C115" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D115" s="22">
+        <v>2001</v>
+      </c>
+      <c r="E115" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F115" s="13">
+        <v>10</v>
+      </c>
+      <c r="G115" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C103" t="s">
-        <v>34</v>
-      </c>
-      <c r="D103">
-        <v>1</v>
-      </c>
-      <c r="E103">
-        <v>999999</v>
-      </c>
-      <c r="F103" s="13">
-        <v>0</v>
-      </c>
-      <c r="G103" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="10">
-        <v>0</v>
+      <c r="C116" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" s="22">
+        <v>1</v>
+      </c>
+      <c r="E116" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F116" s="13">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="G116" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H116" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>4</v>
+      </c>
+      <c r="B117" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>999999</v>
+      </c>
+      <c r="F117" s="13">
+        <v>0</v>
+      </c>
+      <c r="G117" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A118" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D118" s="16">
+        <v>2400.0100000000002</v>
+      </c>
+      <c r="E118" s="16">
+        <v>999999</v>
+      </c>
+      <c r="F118" s="13">
+        <v>30</v>
+      </c>
+      <c r="G118" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="10">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H117" xr:uid="{368F54FD-ED78-4E4A-BD37-CDE3D203AAB7}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="KORBA PAY"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H117">
+      <sortCondition ref="B1:B117"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/config/sla_targets.xlsx
+++ b/config/sla_targets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P.acquahrockson\Desktop\Sla-tracker\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD1024E-BAA3-4785-B920-0135BE53DA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD67492-452E-45F1-9804-65A30F616E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="SMB" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Corporate!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Corporate!$A$1:$H$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Retail!$A$1:$H$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="90">
   <si>
     <t>Name</t>
   </si>
@@ -292,6 +292,24 @@
   </si>
   <si>
     <t>Loyalty Insurance Disbursement</t>
+  </si>
+  <si>
+    <t>AFWEST INTERNATIONAL SECURITY</t>
+  </si>
+  <si>
+    <t>Progressive Security Co. Ltd</t>
+  </si>
+  <si>
+    <t>EBENEZER THOMPSON MEMORIAL SCHOOL</t>
+  </si>
+  <si>
+    <t>Ghana Gas Senior Staff Association Cooperative Credit Union</t>
+  </si>
+  <si>
+    <t>LIFELINE FOR CHILDHOOD CANCER GHANA</t>
+  </si>
+  <si>
+    <t>Loyalty Insurance Claims</t>
   </si>
 </sst>
 </file>
@@ -303,7 +321,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,6 +342,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Californian FB"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -333,7 +357,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -385,12 +409,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -439,20 +487,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
@@ -460,6 +508,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -743,8 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368F54FD-ED78-4E4A-BD37-CDE3D203AAB7}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultColWidth="25.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -783,7 +834,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -809,7 +860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -835,7 +886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -861,7 +912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -887,7 +938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
@@ -913,7 +964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
@@ -939,7 +990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
@@ -965,7 +1016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -991,7 +1042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
@@ -1017,7 +1068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
@@ -1043,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -1069,7 +1120,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
@@ -1095,7 +1146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
         <v>3</v>
       </c>
@@ -1121,7 +1172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
         <v>3</v>
       </c>
@@ -1147,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>3</v>
       </c>
@@ -1173,7 +1224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
         <v>3</v>
       </c>
@@ -1225,7 +1276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
         <v>3</v>
       </c>
@@ -1251,7 +1302,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -1303,7 +1354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
         <v>4</v>
       </c>
@@ -1329,7 +1380,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
         <v>3</v>
       </c>
@@ -1355,7 +1406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
         <v>3</v>
       </c>
@@ -1381,7 +1432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="19" t="s">
         <v>3</v>
       </c>
@@ -1408,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
         <v>3</v>
       </c>
@@ -1434,7 +1485,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
         <v>4</v>
       </c>
@@ -1460,7 +1511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="19" t="s">
         <v>4</v>
       </c>
@@ -1486,7 +1537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="19" t="s">
         <v>4</v>
       </c>
@@ -1512,7 +1563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
         <v>4</v>
       </c>
@@ -1539,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
         <v>3</v>
       </c>
@@ -1565,7 +1616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
         <v>4</v>
       </c>
@@ -1591,7 +1642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
         <v>3</v>
       </c>
@@ -1618,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
         <v>4</v>
       </c>
@@ -1645,7 +1696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
         <v>3</v>
       </c>
@@ -1671,7 +1722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
         <v>3</v>
       </c>
@@ -1697,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
         <v>4</v>
       </c>
@@ -1723,7 +1774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="19" t="s">
         <v>81</v>
       </c>
@@ -1750,7 +1801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="15" t="s">
         <v>4</v>
       </c>
@@ -1776,7 +1827,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
         <v>3</v>
       </c>
@@ -1802,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="15" t="s">
         <v>4</v>
       </c>
@@ -1828,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="15" t="s">
         <v>4</v>
       </c>
@@ -1854,7 +1905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="15" t="s">
         <v>4</v>
       </c>
@@ -1880,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="15" t="s">
         <v>4</v>
       </c>
@@ -1906,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="15" t="s">
         <v>4</v>
       </c>
@@ -1932,7 +1983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="15" t="s">
         <v>4</v>
       </c>
@@ -1958,7 +2009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="15" t="s">
         <v>3</v>
       </c>
@@ -1984,7 +2035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
         <v>3</v>
       </c>
@@ -2010,7 +2061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
         <v>3</v>
       </c>
@@ -2036,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="15" t="s">
         <v>3</v>
       </c>
@@ -2062,7 +2113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="15" t="s">
         <v>3</v>
       </c>
@@ -2088,7 +2139,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="15" t="s">
         <v>3</v>
       </c>
@@ -2115,7 +2166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="15" t="s">
         <v>4</v>
       </c>
@@ -2142,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="15" t="s">
         <v>3</v>
       </c>
@@ -2168,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="15" t="s">
         <v>3</v>
       </c>
@@ -2194,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="15" t="s">
         <v>3</v>
       </c>
@@ -2220,7 +2271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="15" t="s">
         <v>4</v>
       </c>
@@ -2246,7 +2297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="15" t="s">
         <v>3</v>
       </c>
@@ -2272,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="15" t="s">
         <v>3</v>
       </c>
@@ -2298,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="15" t="s">
         <v>3</v>
       </c>
@@ -2324,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="15" t="s">
         <v>3</v>
       </c>
@@ -2350,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="15" t="s">
         <v>3</v>
       </c>
@@ -2376,7 +2427,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
         <v>4</v>
       </c>
@@ -2402,7 +2453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="15" t="s">
         <v>4</v>
       </c>
@@ -2428,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="15" t="s">
         <v>4</v>
       </c>
@@ -2480,7 +2531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="15" t="s">
         <v>3</v>
       </c>
@@ -2507,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="15" t="s">
         <v>4</v>
       </c>
@@ -2533,7 +2584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="15" t="s">
         <v>3</v>
       </c>
@@ -2544,7 +2595,7 @@
         <v>35</v>
       </c>
       <c r="D69" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="16">
         <v>50.99</v>
@@ -2559,7 +2610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="15" t="s">
         <v>3</v>
       </c>
@@ -2585,7 +2636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="15" t="s">
         <v>3</v>
       </c>
@@ -2611,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="15" t="s">
         <v>3</v>
       </c>
@@ -2637,7 +2688,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="19" t="s">
         <v>81</v>
       </c>
@@ -2664,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="15" t="s">
         <v>3</v>
       </c>
@@ -2690,7 +2741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="19" t="s">
         <v>4</v>
       </c>
@@ -2717,7 +2768,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="15" t="s">
         <v>3</v>
       </c>
@@ -2743,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="15" t="s">
         <v>4</v>
       </c>
@@ -2769,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="15" t="s">
         <v>4</v>
       </c>
@@ -2795,7 +2846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="15" t="s">
         <v>3</v>
       </c>
@@ -2822,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="15" t="s">
         <v>3</v>
       </c>
@@ -2849,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="19" t="s">
         <v>4</v>
       </c>
@@ -2875,7 +2926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="15" t="s">
         <v>3</v>
       </c>
@@ -2901,7 +2952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="15" t="s">
         <v>3</v>
       </c>
@@ -2927,7 +2978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="15" t="s">
         <v>3</v>
       </c>
@@ -2953,7 +3004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="15" t="s">
         <v>3</v>
       </c>
@@ -2979,7 +3030,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="15" t="s">
         <v>4</v>
       </c>
@@ -3005,7 +3056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="15" t="s">
         <v>4</v>
       </c>
@@ -3031,7 +3082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="15" t="s">
         <v>4</v>
       </c>
@@ -3057,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="15" t="s">
         <v>4</v>
       </c>
@@ -3083,7 +3134,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="15" t="s">
         <v>4</v>
       </c>
@@ -3110,7 +3161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="15" t="s">
         <v>3</v>
       </c>
@@ -3136,7 +3187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="19" t="s">
         <v>4</v>
       </c>
@@ -3162,7 +3213,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="18" t="s">
         <v>3</v>
       </c>
@@ -3188,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="18" t="s">
         <v>3</v>
       </c>
@@ -3214,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="18" t="s">
         <v>3</v>
       </c>
@@ -3240,7 +3291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>3</v>
       </c>
@@ -3267,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -3294,7 +3345,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="20" t="s">
         <v>3</v>
       </c>
@@ -3320,7 +3371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="19" t="s">
         <v>4</v>
       </c>
@@ -3346,7 +3397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="15" t="s">
         <v>3</v>
       </c>
@@ -3372,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="20" t="s">
         <v>4</v>
       </c>
@@ -3399,7 +3450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="20" t="s">
         <v>3</v>
       </c>
@@ -3425,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -3451,7 +3502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="20" t="s">
         <v>3</v>
       </c>
@@ -3477,7 +3528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="20" t="s">
         <v>40</v>
       </c>
@@ -3503,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="20" t="s">
         <v>3</v>
       </c>
@@ -3529,7 +3580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="20" t="s">
         <v>3</v>
       </c>
@@ -3555,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="20" t="s">
         <v>3</v>
       </c>
@@ -3581,7 +3632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="20" t="s">
         <v>3</v>
       </c>
@@ -3607,7 +3658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="20" t="s">
         <v>3</v>
       </c>
@@ -3633,7 +3684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="5" t="s">
         <v>4</v>
       </c>
@@ -3660,7 +3711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="20" t="s">
         <v>3</v>
       </c>
@@ -3686,7 +3737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="20" t="s">
         <v>3</v>
       </c>
@@ -3712,7 +3763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -3739,7 +3790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -3765,7 +3816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="20" t="s">
         <v>3</v>
       </c>
@@ -3791,7 +3842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -3828,7 +3879,7 @@
         <v>36</v>
       </c>
       <c r="D118" s="16">
-        <v>2400.0100000000002</v>
+        <v>2400</v>
       </c>
       <c r="E118" s="16">
         <v>999999</v>
@@ -3843,17 +3894,346 @@
         <v>30</v>
       </c>
     </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>4</v>
+      </c>
+      <c r="B119" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D119" s="30">
+        <v>0</v>
+      </c>
+      <c r="E119" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F119" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G119" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H119" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C120" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" s="30">
+        <v>0</v>
+      </c>
+      <c r="E120" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F120" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G120" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H120" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C121" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D121" s="30">
+        <v>0</v>
+      </c>
+      <c r="E121" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F121" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G121" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H121" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" s="30">
+        <v>0</v>
+      </c>
+      <c r="E122" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F122" s="13">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="G122" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H122" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>4</v>
+      </c>
+      <c r="B123" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C123" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" s="30">
+        <v>0</v>
+      </c>
+      <c r="E123" s="22">
+        <v>999999</v>
+      </c>
+      <c r="F123" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G123" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H123" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>3</v>
+      </c>
+      <c r="B124" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C124" t="s">
+        <v>35</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>50.99</v>
+      </c>
+      <c r="F124" s="13">
+        <v>1</v>
+      </c>
+      <c r="G124" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>3</v>
+      </c>
+      <c r="B125" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C125" t="s">
+        <v>35</v>
+      </c>
+      <c r="D125">
+        <v>51</v>
+      </c>
+      <c r="E125">
+        <v>100.99</v>
+      </c>
+      <c r="F125" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="G125" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>3</v>
+      </c>
+      <c r="B126" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C126" t="s">
+        <v>35</v>
+      </c>
+      <c r="D126">
+        <v>101</v>
+      </c>
+      <c r="E126">
+        <v>1000.99</v>
+      </c>
+      <c r="F126" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G126" t="b">
+        <v>1</v>
+      </c>
+      <c r="H126" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>3</v>
+      </c>
+      <c r="B127" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C127" t="s">
+        <v>35</v>
+      </c>
+      <c r="D127">
+        <v>1001</v>
+      </c>
+      <c r="E127">
+        <v>2000.99</v>
+      </c>
+      <c r="F127" s="13">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="G127" t="b">
+        <v>1</v>
+      </c>
+      <c r="H127" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>3</v>
+      </c>
+      <c r="B128" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C128" t="s">
+        <v>35</v>
+      </c>
+      <c r="D128">
+        <v>2001</v>
+      </c>
+      <c r="E128">
+        <v>999999</v>
+      </c>
+      <c r="F128" s="13">
+        <v>30</v>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>3</v>
+      </c>
+      <c r="B129" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C129" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>999999</v>
+      </c>
+      <c r="F129" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G129" t="b">
+        <v>1</v>
+      </c>
+      <c r="H129" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>3</v>
+      </c>
+      <c r="B130" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C130" t="s">
+        <v>34</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>999999</v>
+      </c>
+      <c r="F130" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="G130" t="b">
+        <v>1</v>
+      </c>
+      <c r="H130" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>4</v>
+      </c>
+      <c r="B131" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C131" t="s">
+        <v>35</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>999999</v>
+      </c>
+      <c r="F131" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G131" t="b">
+        <v>1</v>
+      </c>
+      <c r="H131" s="10">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H117" xr:uid="{368F54FD-ED78-4E4A-BD37-CDE3D203AAB7}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="KORBA PAY"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H117">
-      <sortCondition ref="B1:B117"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:H131" xr:uid="{368F54FD-ED78-4E4A-BD37-CDE3D203AAB7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4199,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>50.99</v>
@@ -4277,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>50.99</v>
@@ -4355,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>50.99</v>
@@ -4433,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>50.99</v>
@@ -4511,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>50.99</v>
